--- a/research/traditional_assets/database/data/mauritius/mauritius_trucking.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_trucking.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="muse_ubs_i0000" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,113 +589,110 @@
           <t>Trucking</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.0507</v>
-      </c>
-      <c r="E2">
-        <v>0.12</v>
-      </c>
       <c r="G2">
-        <v>-0.138496583143508</v>
+        <v>0.1192307692307692</v>
       </c>
       <c r="H2">
-        <v>-0.138496583143508</v>
+        <v>0.1192307692307692</v>
       </c>
       <c r="I2">
-        <v>-0.2241457858769932</v>
+        <v>0.03593406593406594</v>
       </c>
       <c r="J2">
-        <v>-0.2067572180034326</v>
+        <v>0.02770662821341554</v>
       </c>
       <c r="K2">
-        <v>0.868</v>
+        <v>1.71</v>
       </c>
       <c r="L2">
-        <v>0.1977220956719818</v>
+        <v>0.09395604395604396</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.10934</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.02231428571428571</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.06394152046783626</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.10934</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02231428571428571</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.06394152046783626</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.6879999999999999</v>
+        <v>2.11</v>
       </c>
       <c r="V2">
-        <v>0.1158249158249158</v>
+        <v>0.4306122448979591</v>
       </c>
       <c r="W2">
-        <v>0.06575757575757576</v>
+        <v>0.1757451181911613</v>
       </c>
       <c r="X2">
-        <v>0.1082612993170147</v>
+        <v>0.1169990884211915</v>
       </c>
       <c r="Y2">
-        <v>-0.04250372355943891</v>
+        <v>0.05874602976996984</v>
       </c>
       <c r="Z2">
-        <v>0.2217171717171717</v>
+        <v>2.141176470588235</v>
       </c>
       <c r="AA2">
-        <v>-0.04584162560783177</v>
+        <v>0.05932478040990151</v>
       </c>
       <c r="AB2">
-        <v>0.07705343864794885</v>
+        <v>0.1169990884211915</v>
       </c>
       <c r="AC2">
-        <v>-0.1228950642557806</v>
+        <v>-0.05767430801128999</v>
       </c>
       <c r="AD2">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>4.332</v>
+        <v>-2.11</v>
       </c>
       <c r="AH2">
-        <v>0.4580291970802919</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.2321924144310823</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.4217289719626168</v>
+        <v>-0.7562724014336916</v>
       </c>
       <c r="AK2">
-        <v>0.2069558570609593</v>
+        <v>-0.2456344586728754</v>
       </c>
       <c r="AL2">
-        <v>0.416</v>
+        <v>0.036</v>
       </c>
       <c r="AM2">
-        <v>-0.2510000000000001</v>
+        <v>0.036</v>
       </c>
       <c r="AO2">
-        <v>-2.365384615384615</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="AQ2">
-        <v>3.920318725099601</v>
+        <v>18.16666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +703,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RHT Holding Ltd (MUSE:RHT.I0000)</t>
+          <t>United Bus Service Limited (MUSE:UBS.I0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,113 +711,8822 @@
           <t>Trucking</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0.1192307692307692</v>
+      </c>
+      <c r="H3">
+        <v>0.1192307692307692</v>
+      </c>
+      <c r="I3">
+        <v>0.03593406593406594</v>
+      </c>
+      <c r="J3">
+        <v>0.02770662821341554</v>
+      </c>
+      <c r="K3">
+        <v>1.71</v>
+      </c>
+      <c r="L3">
+        <v>0.09395604395604396</v>
+      </c>
+      <c r="M3">
+        <v>0.10934</v>
+      </c>
+      <c r="N3">
+        <v>0.02231428571428571</v>
+      </c>
+      <c r="O3">
+        <v>0.06394152046783626</v>
+      </c>
+      <c r="P3">
+        <v>0.10934</v>
+      </c>
+      <c r="Q3">
+        <v>0.02231428571428571</v>
+      </c>
+      <c r="R3">
+        <v>0.06394152046783626</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>2.11</v>
+      </c>
+      <c r="V3">
+        <v>0.4306122448979591</v>
+      </c>
+      <c r="W3">
+        <v>0.1757451181911613</v>
+      </c>
+      <c r="X3">
+        <v>0.1169990884211915</v>
+      </c>
+      <c r="Y3">
+        <v>0.05874602976996984</v>
+      </c>
+      <c r="Z3">
+        <v>2.141176470588235</v>
+      </c>
+      <c r="AA3">
+        <v>0.05932478040990151</v>
+      </c>
+      <c r="AB3">
+        <v>0.1169990884211915</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05767430801128999</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-2.11</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.7562724014336916</v>
+      </c>
+      <c r="AK3">
+        <v>-0.2456344586728754</v>
+      </c>
+      <c r="AL3">
+        <v>0.036</v>
+      </c>
+      <c r="AM3">
+        <v>0.036</v>
+      </c>
+      <c r="AO3">
+        <v>18.16666666666667</v>
+      </c>
+      <c r="AQ3">
+        <v>18.16666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>United Bus Service Limited (MUSE:UBS.I0000)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MUSE:UBS.I0000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Trucking</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.27</v>
+      </c>
+      <c r="G2">
+        <v>4.9</v>
+      </c>
+      <c r="H2">
+        <v>3.61954896130393</v>
+      </c>
+      <c r="I2">
+        <v>2.79</v>
+      </c>
+      <c r="J2">
+        <v>2.83254896130393</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1.323</v>
+      </c>
+      <c r="M2">
+        <v>0.116999088421191</v>
+      </c>
+      <c r="N2">
+        <v>0.114211375340133</v>
+      </c>
+      <c r="O2">
+        <v>0.0630631766055046</v>
+      </c>
+      <c r="P2">
+        <v>0.040205</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.116999088421191</v>
+      </c>
+      <c r="T2">
+        <v>0.141583596356347</v>
+      </c>
+      <c r="U2">
+        <v>0.805537710016086</v>
+      </c>
+      <c r="V2">
+        <v>1.05878552432936</v>
+      </c>
+      <c r="W2">
+        <v>10.45097390612341</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>4.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.09707688100614176</v>
+      </c>
+      <c r="AC2">
+        <v>0.07419197247706423</v>
+      </c>
+      <c r="AD2">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>-0.654</v>
+      </c>
+      <c r="AI2">
+        <v>-0.654</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0.036</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>2.11</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1169990884211915</v>
+      </c>
+      <c r="C2">
+        <v>4.9</v>
+      </c>
+      <c r="D2">
+        <v>2.79</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.11</v>
+      </c>
+      <c r="H2">
+        <v>4.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>-0.654</v>
+      </c>
+      <c r="L2">
+        <v>0.654</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.654</v>
+      </c>
+      <c r="O2">
+        <v>0.09810000000000009</v>
+      </c>
+      <c r="P2">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>-0.09810000000000008</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1169990884211915</v>
+      </c>
+      <c r="T2">
+        <v>0.8055377100160859</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1168822397885597</v>
+      </c>
+      <c r="C3">
+        <v>4.852757781276319</v>
+      </c>
       <c r="D3">
-        <v>-0.0507</v>
+        <v>2.791757781276319</v>
       </c>
       <c r="E3">
+        <v>0.049</v>
+      </c>
+      <c r="F3">
+        <v>0.049</v>
+      </c>
+      <c r="G3">
+        <v>2.11</v>
+      </c>
+      <c r="H3">
+        <v>4.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-0.654</v>
+      </c>
+      <c r="L3">
+        <v>0.654</v>
+      </c>
+      <c r="M3">
+        <v>0.0022393</v>
+      </c>
+      <c r="N3">
+        <v>0.6517607</v>
+      </c>
+      <c r="O3">
+        <v>0.09776410500000009</v>
+      </c>
+      <c r="P3">
+        <v>0.5539965949999999</v>
+      </c>
+      <c r="Q3">
+        <v>-0.1000034050000002</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1176704947359189</v>
+      </c>
+      <c r="T3">
+        <v>0.8124539428798603</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>292.0555530746215</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1167653911559279</v>
+      </c>
+      <c r="C4">
+        <v>4.805517778855794</v>
+      </c>
+      <c r="D4">
+        <v>2.793517778855794</v>
+      </c>
+      <c r="E4">
+        <v>0.098</v>
+      </c>
+      <c r="F4">
+        <v>0.098</v>
+      </c>
+      <c r="G4">
+        <v>2.11</v>
+      </c>
+      <c r="H4">
+        <v>4.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-0.654</v>
+      </c>
+      <c r="L4">
+        <v>0.654</v>
+      </c>
+      <c r="M4">
+        <v>0.004478600000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.6495214</v>
+      </c>
+      <c r="O4">
+        <v>0.09742821000000008</v>
+      </c>
+      <c r="P4">
+        <v>0.5520931899999999</v>
+      </c>
+      <c r="Q4">
+        <v>-0.1019068100000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1183556032203346</v>
+      </c>
+      <c r="T4">
+        <v>0.8195113233530997</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>146.0277765373107</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1166485425232961</v>
+      </c>
+      <c r="C5">
+        <v>4.758279996932718</v>
+      </c>
+      <c r="D5">
+        <v>2.795279996932718</v>
+      </c>
+      <c r="E5">
+        <v>0.147</v>
+      </c>
+      <c r="F5">
+        <v>0.147</v>
+      </c>
+      <c r="G5">
+        <v>2.11</v>
+      </c>
+      <c r="H5">
+        <v>4.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-0.654</v>
+      </c>
+      <c r="L5">
+        <v>0.654</v>
+      </c>
+      <c r="M5">
+        <v>0.006717900000000001</v>
+      </c>
+      <c r="N5">
+        <v>0.6472821</v>
+      </c>
+      <c r="O5">
+        <v>0.09709231500000008</v>
+      </c>
+      <c r="P5">
+        <v>0.5501897849999999</v>
+      </c>
+      <c r="Q5">
+        <v>-0.1038102150000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1190548376528826</v>
+      </c>
+      <c r="T5">
+        <v>0.8267142168257871</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>97.35185102487384</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1165316938906643</v>
+      </c>
+      <c r="C6">
+        <v>4.711044439711972</v>
+      </c>
+      <c r="D6">
+        <v>2.797044439711972</v>
+      </c>
+      <c r="E6">
+        <v>0.196</v>
+      </c>
+      <c r="F6">
+        <v>0.196</v>
+      </c>
+      <c r="G6">
+        <v>2.11</v>
+      </c>
+      <c r="H6">
+        <v>4.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-0.654</v>
+      </c>
+      <c r="L6">
+        <v>0.654</v>
+      </c>
+      <c r="M6">
+        <v>0.008957200000000002</v>
+      </c>
+      <c r="N6">
+        <v>0.6450428</v>
+      </c>
+      <c r="O6">
+        <v>0.09675642000000009</v>
+      </c>
+      <c r="P6">
+        <v>0.54828638</v>
+      </c>
+      <c r="Q6">
+        <v>-0.1057136200000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.119768639469442</v>
+      </c>
+      <c r="T6">
+        <v>0.8340671705791556</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>73.01388826865536</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1164148452580326</v>
+      </c>
+      <c r="C7">
+        <v>4.663811111409061</v>
+      </c>
+      <c r="D7">
+        <v>2.798811111409061</v>
+      </c>
+      <c r="E7">
+        <v>0.245</v>
+      </c>
+      <c r="F7">
+        <v>0.245</v>
+      </c>
+      <c r="G7">
+        <v>2.11</v>
+      </c>
+      <c r="H7">
+        <v>4.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-0.654</v>
+      </c>
+      <c r="L7">
+        <v>0.654</v>
+      </c>
+      <c r="M7">
+        <v>0.0111965</v>
+      </c>
+      <c r="N7">
+        <v>0.6428035</v>
+      </c>
+      <c r="O7">
+        <v>0.09642052500000008</v>
+      </c>
+      <c r="P7">
+        <v>0.5463829749999999</v>
+      </c>
+      <c r="Q7">
+        <v>-0.1076170250000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1204974686926659</v>
+      </c>
+      <c r="T7">
+        <v>0.8415749233589108</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>58.4111106149243</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1162979966254008</v>
+      </c>
+      <c r="C8">
+        <v>4.616580016250148</v>
+      </c>
+      <c r="D8">
+        <v>2.800580016250148</v>
+      </c>
+      <c r="E8">
+        <v>0.294</v>
+      </c>
+      <c r="F8">
+        <v>0.294</v>
+      </c>
+      <c r="G8">
+        <v>2.11</v>
+      </c>
+      <c r="H8">
+        <v>4.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-0.654</v>
+      </c>
+      <c r="L8">
+        <v>0.654</v>
+      </c>
+      <c r="M8">
+        <v>0.0134358</v>
+      </c>
+      <c r="N8">
+        <v>0.6405642</v>
+      </c>
+      <c r="O8">
+        <v>0.09608463000000009</v>
+      </c>
+      <c r="P8">
+        <v>0.5444795699999999</v>
+      </c>
+      <c r="Q8">
+        <v>-0.1095204300000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1212418049206391</v>
+      </c>
+      <c r="T8">
+        <v>0.8492424155595117</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>48.67592551243692</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.116181147992769</v>
+      </c>
+      <c r="C9">
+        <v>4.569351158472087</v>
+      </c>
+      <c r="D9">
+        <v>2.802351158472087</v>
+      </c>
+      <c r="E9">
+        <v>0.3430000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.3430000000000001</v>
+      </c>
+      <c r="G9">
+        <v>2.11</v>
+      </c>
+      <c r="H9">
+        <v>4.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>-0.654</v>
+      </c>
+      <c r="L9">
+        <v>0.654</v>
+      </c>
+      <c r="M9">
+        <v>0.0156751</v>
+      </c>
+      <c r="N9">
+        <v>0.6383249</v>
+      </c>
+      <c r="O9">
+        <v>0.09574873500000008</v>
+      </c>
+      <c r="P9">
+        <v>0.5425761649999998</v>
+      </c>
+      <c r="Q9">
+        <v>-0.1114238350000002</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1220021483793215</v>
+      </c>
+      <c r="T9">
+        <v>0.8570748000655021</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>41.72222186780306</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1160642993601372</v>
+      </c>
+      <c r="C10">
+        <v>4.522124542322454</v>
+      </c>
+      <c r="D10">
+        <v>2.804124542322455</v>
+      </c>
+      <c r="E10">
+        <v>0.392</v>
+      </c>
+      <c r="F10">
+        <v>0.392</v>
+      </c>
+      <c r="G10">
+        <v>2.11</v>
+      </c>
+      <c r="H10">
+        <v>4.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-0.654</v>
+      </c>
+      <c r="L10">
+        <v>0.654</v>
+      </c>
+      <c r="M10">
+        <v>0.0179144</v>
+      </c>
+      <c r="N10">
+        <v>0.6360856</v>
+      </c>
+      <c r="O10">
+        <v>0.0954128400000001</v>
+      </c>
+      <c r="P10">
+        <v>0.54067276</v>
+      </c>
+      <c r="Q10">
+        <v>-0.1133272400000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1227790210436274</v>
+      </c>
+      <c r="T10">
+        <v>0.8650774537998835</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>36.50694413432768</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1159474507275054</v>
+      </c>
+      <c r="C11">
+        <v>4.474900172059589</v>
+      </c>
+      <c r="D11">
+        <v>2.805900172059589</v>
+      </c>
+      <c r="E11">
+        <v>0.441</v>
+      </c>
+      <c r="F11">
+        <v>0.441</v>
+      </c>
+      <c r="G11">
+        <v>2.11</v>
+      </c>
+      <c r="H11">
+        <v>4.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-0.654</v>
+      </c>
+      <c r="L11">
+        <v>0.654</v>
+      </c>
+      <c r="M11">
+        <v>0.0201537</v>
+      </c>
+      <c r="N11">
+        <v>0.6338463</v>
+      </c>
+      <c r="O11">
+        <v>0.09507694500000008</v>
+      </c>
+      <c r="P11">
+        <v>0.5387693549999999</v>
+      </c>
+      <c r="Q11">
+        <v>-0.1152306450000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1235729678324235</v>
+      </c>
+      <c r="T11">
+        <v>0.8732559900339216</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>32.45061700829127</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1158306020948736</v>
+      </c>
+      <c r="C12">
+        <v>4.427678051952618</v>
+      </c>
+      <c r="D12">
+        <v>2.807678051952619</v>
+      </c>
+      <c r="E12">
+        <v>0.49</v>
+      </c>
+      <c r="F12">
+        <v>0.49</v>
+      </c>
+      <c r="G12">
+        <v>2.11</v>
+      </c>
+      <c r="H12">
+        <v>4.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-0.654</v>
+      </c>
+      <c r="L12">
+        <v>0.654</v>
+      </c>
+      <c r="M12">
+        <v>0.022393</v>
+      </c>
+      <c r="N12">
+        <v>0.631607</v>
+      </c>
+      <c r="O12">
+        <v>0.09474105000000009</v>
+      </c>
+      <c r="P12">
+        <v>0.5368659499999999</v>
+      </c>
+      <c r="Q12">
+        <v>-0.1171340500000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1243845578831929</v>
+      </c>
+      <c r="T12">
+        <v>0.8816162715176051</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>29.20555530746215</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1157137534622418</v>
+      </c>
+      <c r="C13">
+        <v>4.3804581862815</v>
+      </c>
+      <c r="D13">
+        <v>2.8094581862815</v>
+      </c>
+      <c r="E13">
+        <v>0.539</v>
+      </c>
+      <c r="F13">
+        <v>0.539</v>
+      </c>
+      <c r="G13">
+        <v>2.11</v>
+      </c>
+      <c r="H13">
+        <v>4.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-0.654</v>
+      </c>
+      <c r="L13">
+        <v>0.654</v>
+      </c>
+      <c r="M13">
+        <v>0.0246323</v>
+      </c>
+      <c r="N13">
+        <v>0.6293677</v>
+      </c>
+      <c r="O13">
+        <v>0.09440515500000007</v>
+      </c>
+      <c r="P13">
+        <v>0.534962545</v>
+      </c>
+      <c r="Q13">
+        <v>-0.1190374550000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1252143859126313</v>
+      </c>
+      <c r="T13">
+        <v>0.8901644244953039</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>26.55050482496559</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
         <v>0.12</v>
       </c>
-      <c r="G3">
-        <v>-0.138496583143508</v>
-      </c>
-      <c r="H3">
-        <v>-0.138496583143508</v>
-      </c>
-      <c r="I3">
-        <v>-0.2241457858769932</v>
-      </c>
-      <c r="J3">
-        <v>-0.2067572180034326</v>
-      </c>
-      <c r="K3">
-        <v>0.868</v>
-      </c>
-      <c r="L3">
-        <v>0.1977220956719818</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>-0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>-0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="V3">
-        <v>0.1158249158249158</v>
-      </c>
-      <c r="W3">
-        <v>0.06575757575757576</v>
-      </c>
-      <c r="X3">
-        <v>0.1082612993170147</v>
-      </c>
-      <c r="Y3">
-        <v>-0.04250372355943891</v>
-      </c>
-      <c r="Z3">
-        <v>0.2217171717171717</v>
-      </c>
-      <c r="AA3">
-        <v>-0.04584162560783177</v>
-      </c>
-      <c r="AB3">
-        <v>0.07705343864794885</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1228950642557806</v>
-      </c>
-      <c r="AD3">
-        <v>5.02</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>5.02</v>
-      </c>
-      <c r="AG3">
-        <v>4.332</v>
-      </c>
-      <c r="AH3">
-        <v>0.4580291970802919</v>
-      </c>
-      <c r="AI3">
-        <v>0.2321924144310823</v>
-      </c>
-      <c r="AJ3">
-        <v>0.4217289719626168</v>
-      </c>
-      <c r="AK3">
-        <v>0.2069558570609593</v>
-      </c>
-      <c r="AL3">
-        <v>0.416</v>
-      </c>
-      <c r="AM3">
-        <v>-0.2510000000000001</v>
-      </c>
-      <c r="AO3">
-        <v>-2.365384615384615</v>
-      </c>
-      <c r="AQ3">
-        <v>3.920318725099601</v>
+      <c r="B14">
+        <v>0.1155969048296101</v>
+      </c>
+      <c r="C14">
+        <v>4.333240579337051</v>
+      </c>
+      <c r="D14">
+        <v>2.811240579337051</v>
+      </c>
+      <c r="E14">
+        <v>0.588</v>
+      </c>
+      <c r="F14">
+        <v>0.588</v>
+      </c>
+      <c r="G14">
+        <v>2.11</v>
+      </c>
+      <c r="H14">
+        <v>4.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-0.654</v>
+      </c>
+      <c r="L14">
+        <v>0.654</v>
+      </c>
+      <c r="M14">
+        <v>0.0268716</v>
+      </c>
+      <c r="N14">
+        <v>0.6271284</v>
+      </c>
+      <c r="O14">
+        <v>0.09406926000000009</v>
+      </c>
+      <c r="P14">
+        <v>0.53305914</v>
+      </c>
+      <c r="Q14">
+        <v>-0.12094086</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1260630736700114</v>
+      </c>
+      <c r="T14">
+        <v>0.8989068536770414</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>24.33796275621846</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1154800561969782</v>
+      </c>
+      <c r="C15">
+        <v>4.286025235420984</v>
+      </c>
+      <c r="D15">
+        <v>2.813025235420985</v>
+      </c>
+      <c r="E15">
+        <v>0.6370000000000001</v>
+      </c>
+      <c r="F15">
+        <v>0.6370000000000001</v>
+      </c>
+      <c r="G15">
+        <v>2.11</v>
+      </c>
+      <c r="H15">
+        <v>4.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-0.654</v>
+      </c>
+      <c r="L15">
+        <v>0.654</v>
+      </c>
+      <c r="M15">
+        <v>0.02911090000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.6248891</v>
+      </c>
+      <c r="O15">
+        <v>0.09373336500000008</v>
+      </c>
+      <c r="P15">
+        <v>0.5311557349999999</v>
+      </c>
+      <c r="Q15">
+        <v>-0.1228442650000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1269312714907796</v>
+      </c>
+      <c r="T15">
+        <v>0.9078502582422668</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.038845</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>22.46581177497088</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1153632075643465</v>
+      </c>
+      <c r="C16">
+        <v>4.238812158845944</v>
+      </c>
+      <c r="D16">
+        <v>2.814812158845944</v>
+      </c>
+      <c r="E16">
+        <v>0.6860000000000002</v>
+      </c>
+      <c r="F16">
+        <v>0.6860000000000002</v>
+      </c>
+      <c r="G16">
+        <v>2.11</v>
+      </c>
+      <c r="H16">
+        <v>4.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-0.654</v>
+      </c>
+      <c r="L16">
+        <v>0.654</v>
+      </c>
+      <c r="M16">
+        <v>0.03135020000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.6226498</v>
+      </c>
+      <c r="O16">
+        <v>0.09339747000000009</v>
+      </c>
+      <c r="P16">
+        <v>0.5292523299999999</v>
+      </c>
+      <c r="Q16">
+        <v>-0.1247476700000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1278196599585424</v>
+      </c>
+      <c r="T16">
+        <v>0.9170016489601721</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.038845</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>20.86111093390153</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1152463589317147</v>
+      </c>
+      <c r="C17">
+        <v>4.191601353935538</v>
+      </c>
+      <c r="D17">
+        <v>2.816601353935538</v>
+      </c>
+      <c r="E17">
+        <v>0.735</v>
+      </c>
+      <c r="F17">
+        <v>0.735</v>
+      </c>
+      <c r="G17">
+        <v>2.11</v>
+      </c>
+      <c r="H17">
+        <v>4.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-0.654</v>
+      </c>
+      <c r="L17">
+        <v>0.654</v>
+      </c>
+      <c r="M17">
+        <v>0.0335895</v>
+      </c>
+      <c r="N17">
+        <v>0.6204105</v>
+      </c>
+      <c r="O17">
+        <v>0.09306157500000008</v>
+      </c>
+      <c r="P17">
+        <v>0.5273489249999999</v>
+      </c>
+      <c r="Q17">
+        <v>-0.1266510750000002</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1287289516843702</v>
+      </c>
+      <c r="T17">
+        <v>0.9263683665184986</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.038845</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>19.47037020497477</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1151295102990829</v>
+      </c>
+      <c r="C18">
+        <v>4.144392825024376</v>
+      </c>
+      <c r="D18">
+        <v>2.818392825024376</v>
+      </c>
+      <c r="E18">
+        <v>0.784</v>
+      </c>
+      <c r="F18">
+        <v>0.784</v>
+      </c>
+      <c r="G18">
+        <v>2.11</v>
+      </c>
+      <c r="H18">
+        <v>4.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-0.654</v>
+      </c>
+      <c r="L18">
+        <v>0.654</v>
+      </c>
+      <c r="M18">
+        <v>0.03582880000000001</v>
+      </c>
+      <c r="N18">
+        <v>0.6181712</v>
+      </c>
+      <c r="O18">
+        <v>0.09272568000000009</v>
+      </c>
+      <c r="P18">
+        <v>0.5254455199999999</v>
+      </c>
+      <c r="Q18">
+        <v>-0.1285544800000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1296598932131939</v>
+      </c>
+      <c r="T18">
+        <v>0.9359581011615473</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W18">
+        <v>0.038845</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>18.25347206716384</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1150126616664511</v>
+      </c>
+      <c r="C19">
+        <v>4.0971865764581</v>
+      </c>
+      <c r="D19">
+        <v>2.8201865764581</v>
+      </c>
+      <c r="E19">
+        <v>0.8330000000000001</v>
+      </c>
+      <c r="F19">
+        <v>0.8330000000000001</v>
+      </c>
+      <c r="G19">
+        <v>2.11</v>
+      </c>
+      <c r="H19">
+        <v>4.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-0.654</v>
+      </c>
+      <c r="L19">
+        <v>0.654</v>
+      </c>
+      <c r="M19">
+        <v>0.03806810000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.6159319</v>
+      </c>
+      <c r="O19">
+        <v>0.09238978500000009</v>
+      </c>
+      <c r="P19">
+        <v>0.5235421149999999</v>
+      </c>
+      <c r="Q19">
+        <v>-0.1304578850000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1306132670680134</v>
+      </c>
+      <c r="T19">
+        <v>0.945778913747802</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W19">
+        <v>0.038845</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>17.1797384161542</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1148958130338193</v>
+      </c>
+      <c r="C20">
+        <v>4.049982612593426</v>
+      </c>
+      <c r="D20">
+        <v>2.821982612593426</v>
+      </c>
+      <c r="E20">
+        <v>0.882</v>
+      </c>
+      <c r="F20">
+        <v>0.882</v>
+      </c>
+      <c r="G20">
+        <v>2.11</v>
+      </c>
+      <c r="H20">
+        <v>4.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-0.654</v>
+      </c>
+      <c r="L20">
+        <v>0.654</v>
+      </c>
+      <c r="M20">
+        <v>0.04030740000000001</v>
+      </c>
+      <c r="N20">
+        <v>0.6136926</v>
+      </c>
+      <c r="O20">
+        <v>0.09205389000000008</v>
+      </c>
+      <c r="P20">
+        <v>0.5216387099999999</v>
+      </c>
+      <c r="Q20">
+        <v>-0.1323612900000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1315898939436821</v>
+      </c>
+      <c r="T20">
+        <v>0.9558392583483555</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.038845</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>16.22530850414564</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1147789644011875</v>
+      </c>
+      <c r="C21">
+        <v>4.00278093779817</v>
+      </c>
+      <c r="D21">
+        <v>2.82378093779817</v>
+      </c>
+      <c r="E21">
+        <v>0.931</v>
+      </c>
+      <c r="F21">
+        <v>0.931</v>
+      </c>
+      <c r="G21">
+        <v>2.11</v>
+      </c>
+      <c r="H21">
+        <v>4.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-0.654</v>
+      </c>
+      <c r="L21">
+        <v>0.654</v>
+      </c>
+      <c r="M21">
+        <v>0.04254670000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.6114533</v>
+      </c>
+      <c r="O21">
+        <v>0.09171799500000008</v>
+      </c>
+      <c r="P21">
+        <v>0.5197353049999999</v>
+      </c>
+      <c r="Q21">
+        <v>-0.1342646950000002</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1325906350631945</v>
+      </c>
+      <c r="T21">
+        <v>0.966148006519293</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W21">
+        <v>0.038845</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>15.37134489866429</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1146621157685558</v>
+      </c>
+      <c r="C22">
+        <v>3.955581556451295</v>
+      </c>
+      <c r="D22">
+        <v>2.825581556451295</v>
+      </c>
+      <c r="E22">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="F22">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="G22">
+        <v>2.11</v>
+      </c>
+      <c r="H22">
+        <v>4.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-0.654</v>
+      </c>
+      <c r="L22">
+        <v>0.654</v>
+      </c>
+      <c r="M22">
+        <v>0.04478600000000001</v>
+      </c>
+      <c r="N22">
+        <v>0.609214</v>
+      </c>
+      <c r="O22">
+        <v>0.09138210000000009</v>
+      </c>
+      <c r="P22">
+        <v>0.5178318999999999</v>
+      </c>
+      <c r="Q22">
+        <v>-0.1361681000000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1336163947106947</v>
+      </c>
+      <c r="T22">
+        <v>0.976714473394504</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W22">
+        <v>0.038845</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>14.60277765373108</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1145452671359239</v>
+      </c>
+      <c r="C23">
+        <v>3.908384472942936</v>
+      </c>
+      <c r="D23">
+        <v>2.827384472942936</v>
+      </c>
+      <c r="E23">
+        <v>1.029</v>
+      </c>
+      <c r="F23">
+        <v>1.029</v>
+      </c>
+      <c r="G23">
+        <v>2.11</v>
+      </c>
+      <c r="H23">
+        <v>4.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-0.654</v>
+      </c>
+      <c r="L23">
+        <v>0.654</v>
+      </c>
+      <c r="M23">
+        <v>0.04702530000000001</v>
+      </c>
+      <c r="N23">
+        <v>0.6069747</v>
+      </c>
+      <c r="O23">
+        <v>0.09104620500000007</v>
+      </c>
+      <c r="P23">
+        <v>0.5159284949999999</v>
+      </c>
+      <c r="Q23">
+        <v>-0.1380715050000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1346681229568658</v>
+      </c>
+      <c r="T23">
+        <v>0.9875484457602267</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W23">
+        <v>0.038845</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>13.90740728926769</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1144284185032922</v>
+      </c>
+      <c r="C24">
+        <v>3.861189691674439</v>
+      </c>
+      <c r="D24">
+        <v>2.82918969167444</v>
+      </c>
+      <c r="E24">
+        <v>1.078</v>
+      </c>
+      <c r="F24">
+        <v>1.078</v>
+      </c>
+      <c r="G24">
+        <v>2.11</v>
+      </c>
+      <c r="H24">
+        <v>4.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-0.654</v>
+      </c>
+      <c r="L24">
+        <v>0.654</v>
+      </c>
+      <c r="M24">
+        <v>0.04926460000000001</v>
+      </c>
+      <c r="N24">
+        <v>0.6047354</v>
+      </c>
+      <c r="O24">
+        <v>0.09071031000000009</v>
+      </c>
+      <c r="P24">
+        <v>0.51402509</v>
+      </c>
+      <c r="Q24">
+        <v>-0.1399749100000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1357468185939643</v>
+      </c>
+      <c r="T24">
+        <v>0.9986602122891731</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W24">
+        <v>0.038845</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>13.2752524124828</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1146243698706604</v>
+      </c>
+      <c r="C25">
+        <v>3.809163705488534</v>
+      </c>
+      <c r="D25">
+        <v>2.826163705488534</v>
+      </c>
+      <c r="E25">
+        <v>1.127</v>
+      </c>
+      <c r="F25">
+        <v>1.127</v>
+      </c>
+      <c r="G25">
+        <v>2.11</v>
+      </c>
+      <c r="H25">
+        <v>4.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-0.654</v>
+      </c>
+      <c r="L25">
+        <v>0.654</v>
+      </c>
+      <c r="M25">
+        <v>0.05330710000000001</v>
+      </c>
+      <c r="N25">
+        <v>0.6006929</v>
+      </c>
+      <c r="O25">
+        <v>0.09010393500000008</v>
+      </c>
+      <c r="P25">
+        <v>0.510588965</v>
+      </c>
+      <c r="Q25">
+        <v>-0.1434110350000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1368535322995589</v>
+      </c>
+      <c r="T25">
+        <v>1.01006059613056</v>
+      </c>
+      <c r="U25">
+        <v>0.0473</v>
+      </c>
+      <c r="V25">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W25">
+        <v>0.040205</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>12.26853458544922</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1145211212380286</v>
+      </c>
+      <c r="C26">
+        <v>3.761757319059978</v>
+      </c>
+      <c r="D26">
+        <v>2.827757319059978</v>
+      </c>
+      <c r="E26">
+        <v>1.176</v>
+      </c>
+      <c r="F26">
+        <v>1.176</v>
+      </c>
+      <c r="G26">
+        <v>2.11</v>
+      </c>
+      <c r="H26">
+        <v>4.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>-0.654</v>
+      </c>
+      <c r="L26">
+        <v>0.654</v>
+      </c>
+      <c r="M26">
+        <v>0.0556248</v>
+      </c>
+      <c r="N26">
+        <v>0.5983752</v>
+      </c>
+      <c r="O26">
+        <v>0.08975628000000008</v>
+      </c>
+      <c r="P26">
+        <v>0.50861892</v>
+      </c>
+      <c r="Q26">
+        <v>-0.1453810800000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1379893700500376</v>
+      </c>
+      <c r="T26">
+        <v>1.021760990073035</v>
+      </c>
+      <c r="U26">
+        <v>0.0473</v>
+      </c>
+      <c r="V26">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W26">
+        <v>0.040205</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>11.75734564438883</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1144178726053968</v>
+      </c>
+      <c r="C27">
+        <v>3.714352730854962</v>
+      </c>
+      <c r="D27">
+        <v>2.829352730854962</v>
+      </c>
+      <c r="E27">
+        <v>1.225</v>
+      </c>
+      <c r="F27">
+        <v>1.225</v>
+      </c>
+      <c r="G27">
+        <v>2.11</v>
+      </c>
+      <c r="H27">
+        <v>4.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-0.654</v>
+      </c>
+      <c r="L27">
+        <v>0.654</v>
+      </c>
+      <c r="M27">
+        <v>0.05794250000000001</v>
+      </c>
+      <c r="N27">
+        <v>0.5960575</v>
+      </c>
+      <c r="O27">
+        <v>0.08940862500000009</v>
+      </c>
+      <c r="P27">
+        <v>0.5066488749999999</v>
+      </c>
+      <c r="Q27">
+        <v>-0.1473511250000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1391554968071957</v>
+      </c>
+      <c r="T27">
+        <v>1.033773394520644</v>
+      </c>
+      <c r="U27">
+        <v>0.0473</v>
+      </c>
+      <c r="V27">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W27">
+        <v>0.040205</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>11.28705181861328</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.114314623972765</v>
+      </c>
+      <c r="C28">
+        <v>3.666949943918859</v>
+      </c>
+      <c r="D28">
+        <v>2.83094994391886</v>
+      </c>
+      <c r="E28">
+        <v>1.274</v>
+      </c>
+      <c r="F28">
+        <v>1.274</v>
+      </c>
+      <c r="G28">
+        <v>2.11</v>
+      </c>
+      <c r="H28">
+        <v>4.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-0.654</v>
+      </c>
+      <c r="L28">
+        <v>0.654</v>
+      </c>
+      <c r="M28">
+        <v>0.06026020000000001</v>
+      </c>
+      <c r="N28">
+        <v>0.5937398</v>
+      </c>
+      <c r="O28">
+        <v>0.08906097000000009</v>
+      </c>
+      <c r="P28">
+        <v>0.5046788299999999</v>
+      </c>
+      <c r="Q28">
+        <v>-0.1493211700000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1403531405037365</v>
+      </c>
+      <c r="T28">
+        <v>1.046110458547917</v>
+      </c>
+      <c r="U28">
+        <v>0.0473</v>
+      </c>
+      <c r="V28">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.040205</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>10.85293444097431</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1142113753401332</v>
+      </c>
+      <c r="C29">
+        <v>3.619548961303927</v>
+      </c>
+      <c r="D29">
+        <v>2.832548961303928</v>
+      </c>
+      <c r="E29">
+        <v>1.323</v>
+      </c>
+      <c r="F29">
+        <v>1.323</v>
+      </c>
+      <c r="G29">
+        <v>2.11</v>
+      </c>
+      <c r="H29">
+        <v>4.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-0.654</v>
+      </c>
+      <c r="L29">
+        <v>0.654</v>
+      </c>
+      <c r="M29">
+        <v>0.06257790000000001</v>
+      </c>
+      <c r="N29">
+        <v>0.5914221000000001</v>
+      </c>
+      <c r="O29">
+        <v>0.08871331500000008</v>
+      </c>
+      <c r="P29">
+        <v>0.5027087849999999</v>
+      </c>
+      <c r="Q29">
+        <v>-0.1512912150000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1415835963563469</v>
+      </c>
+      <c r="T29">
+        <v>1.058785524329362</v>
+      </c>
+      <c r="U29">
+        <v>0.0473</v>
+      </c>
+      <c r="V29">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W29">
+        <v>0.040205</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>10.45097390612341</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1150125267075014</v>
+      </c>
+      <c r="C30">
+        <v>3.55818864954235</v>
+      </c>
+      <c r="D30">
+        <v>2.82018864954235</v>
+      </c>
+      <c r="E30">
+        <v>1.372</v>
+      </c>
+      <c r="F30">
+        <v>1.372</v>
+      </c>
+      <c r="G30">
+        <v>2.11</v>
+      </c>
+      <c r="H30">
+        <v>4.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>-0.654</v>
+      </c>
+      <c r="L30">
+        <v>0.654</v>
+      </c>
+      <c r="M30">
+        <v>0.07010920000000001</v>
+      </c>
+      <c r="N30">
+        <v>0.5838908</v>
+      </c>
+      <c r="O30">
+        <v>0.08758362000000008</v>
+      </c>
+      <c r="P30">
+        <v>0.49630718</v>
+      </c>
+      <c r="Q30">
+        <v>-0.1576928200000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1428482315381965</v>
+      </c>
+      <c r="T30">
+        <v>1.071812675271403</v>
+      </c>
+      <c r="U30">
+        <v>0.0511</v>
+      </c>
+      <c r="V30">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W30">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>9.328304987077301</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1149415780748697</v>
+      </c>
+      <c r="C31">
+        <v>3.510278902999388</v>
+      </c>
+      <c r="D31">
+        <v>2.821278902999389</v>
+      </c>
+      <c r="E31">
+        <v>1.421</v>
+      </c>
+      <c r="F31">
+        <v>1.421</v>
+      </c>
+      <c r="G31">
+        <v>2.11</v>
+      </c>
+      <c r="H31">
+        <v>4.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>-0.654</v>
+      </c>
+      <c r="L31">
+        <v>0.654</v>
+      </c>
+      <c r="M31">
+        <v>0.0726131</v>
+      </c>
+      <c r="N31">
+        <v>0.5813869</v>
+      </c>
+      <c r="O31">
+        <v>0.08720803500000009</v>
+      </c>
+      <c r="P31">
+        <v>0.494178865</v>
+      </c>
+      <c r="Q31">
+        <v>-0.1598211350000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1441484902462953</v>
+      </c>
+      <c r="T31">
+        <v>1.085206788211811</v>
+      </c>
+      <c r="U31">
+        <v>0.0511</v>
+      </c>
+      <c r="V31">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W31">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>9.006639297867741</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1148706294422379</v>
+      </c>
+      <c r="C32">
+        <v>3.462369999742068</v>
+      </c>
+      <c r="D32">
+        <v>2.822369999742069</v>
+      </c>
+      <c r="E32">
+        <v>1.47</v>
+      </c>
+      <c r="F32">
+        <v>1.47</v>
+      </c>
+      <c r="G32">
+        <v>2.11</v>
+      </c>
+      <c r="H32">
+        <v>4.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>-0.654</v>
+      </c>
+      <c r="L32">
+        <v>0.654</v>
+      </c>
+      <c r="M32">
+        <v>0.075117</v>
+      </c>
+      <c r="N32">
+        <v>0.578883</v>
+      </c>
+      <c r="O32">
+        <v>0.08683245000000009</v>
+      </c>
+      <c r="P32">
+        <v>0.49205055</v>
+      </c>
+      <c r="Q32">
+        <v>-0.1619494500000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.145485899203197</v>
+      </c>
+      <c r="T32">
+        <v>1.098983590093374</v>
+      </c>
+      <c r="U32">
+        <v>0.0511</v>
+      </c>
+      <c r="V32">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W32">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>8.706417987938815</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1147996808096061</v>
+      </c>
+      <c r="C33">
+        <v>3.414461940749163</v>
+      </c>
+      <c r="D33">
+        <v>2.823461940749163</v>
+      </c>
+      <c r="E33">
+        <v>1.519</v>
+      </c>
+      <c r="F33">
+        <v>1.519</v>
+      </c>
+      <c r="G33">
+        <v>2.11</v>
+      </c>
+      <c r="H33">
+        <v>4.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>-0.654</v>
+      </c>
+      <c r="L33">
+        <v>0.654</v>
+      </c>
+      <c r="M33">
+        <v>0.07762090000000001</v>
+      </c>
+      <c r="N33">
+        <v>0.5763791</v>
+      </c>
+      <c r="O33">
+        <v>0.08645686500000008</v>
+      </c>
+      <c r="P33">
+        <v>0.489922235</v>
+      </c>
+      <c r="Q33">
+        <v>-0.164077765</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1468620736371103</v>
+      </c>
+      <c r="T33">
+        <v>1.113159719565707</v>
+      </c>
+      <c r="U33">
+        <v>0.0511</v>
+      </c>
+      <c r="V33">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W33">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.425565794779498</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1147287321769743</v>
+      </c>
+      <c r="C34">
+        <v>3.366554727000957</v>
+      </c>
+      <c r="D34">
+        <v>2.824554727000958</v>
+      </c>
+      <c r="E34">
+        <v>1.568</v>
+      </c>
+      <c r="F34">
+        <v>1.568</v>
+      </c>
+      <c r="G34">
+        <v>2.11</v>
+      </c>
+      <c r="H34">
+        <v>4.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>-0.654</v>
+      </c>
+      <c r="L34">
+        <v>0.654</v>
+      </c>
+      <c r="M34">
+        <v>0.0801248</v>
+      </c>
+      <c r="N34">
+        <v>0.5738752</v>
+      </c>
+      <c r="O34">
+        <v>0.08608128000000008</v>
+      </c>
+      <c r="P34">
+        <v>0.4877939199999999</v>
+      </c>
+      <c r="Q34">
+        <v>-0.1662060800000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1482787237896681</v>
+      </c>
+      <c r="T34">
+        <v>1.12775279402252</v>
+      </c>
+      <c r="U34">
+        <v>0.0511</v>
+      </c>
+      <c r="V34">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W34">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>8.16226686369264</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1146577835443425</v>
+      </c>
+      <c r="C35">
+        <v>3.318648359479256</v>
+      </c>
+      <c r="D35">
+        <v>2.825648359479256</v>
+      </c>
+      <c r="E35">
+        <v>1.617</v>
+      </c>
+      <c r="F35">
+        <v>1.617</v>
+      </c>
+      <c r="G35">
+        <v>2.11</v>
+      </c>
+      <c r="H35">
+        <v>4.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-0.654</v>
+      </c>
+      <c r="L35">
+        <v>0.654</v>
+      </c>
+      <c r="M35">
+        <v>0.08262870000000001</v>
+      </c>
+      <c r="N35">
+        <v>0.5713713</v>
+      </c>
+      <c r="O35">
+        <v>0.08570569500000008</v>
+      </c>
+      <c r="P35">
+        <v>0.4856656049999999</v>
+      </c>
+      <c r="Q35">
+        <v>-0.1683343950000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1497376620064814</v>
+      </c>
+      <c r="T35">
+        <v>1.142781482642223</v>
+      </c>
+      <c r="U35">
+        <v>0.0511</v>
+      </c>
+      <c r="V35">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W35">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>7.91492544358074</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1151359349117107</v>
+      </c>
+      <c r="C36">
+        <v>3.262294266527909</v>
+      </c>
+      <c r="D36">
+        <v>2.818294266527909</v>
+      </c>
+      <c r="E36">
+        <v>1.666</v>
+      </c>
+      <c r="F36">
+        <v>1.666</v>
+      </c>
+      <c r="G36">
+        <v>2.11</v>
+      </c>
+      <c r="H36">
+        <v>4.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>-0.654</v>
+      </c>
+      <c r="L36">
+        <v>0.654</v>
+      </c>
+      <c r="M36">
+        <v>0.08829800000000002</v>
+      </c>
+      <c r="N36">
+        <v>0.565702</v>
+      </c>
+      <c r="O36">
+        <v>0.08485530000000008</v>
+      </c>
+      <c r="P36">
+        <v>0.4808467</v>
+      </c>
+      <c r="Q36">
+        <v>-0.1731533000000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.151240810472289</v>
+      </c>
+      <c r="T36">
+        <v>1.158265586068584</v>
+      </c>
+      <c r="U36">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W36">
+        <v>0.04505</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.406736279417427</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1150811362790789</v>
+      </c>
+      <c r="C37">
+        <v>3.214135141091057</v>
+      </c>
+      <c r="D37">
+        <v>2.819135141091058</v>
+      </c>
+      <c r="E37">
+        <v>1.715</v>
+      </c>
+      <c r="F37">
+        <v>1.715</v>
+      </c>
+      <c r="G37">
+        <v>2.11</v>
+      </c>
+      <c r="H37">
+        <v>4.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>-0.654</v>
+      </c>
+      <c r="L37">
+        <v>0.654</v>
+      </c>
+      <c r="M37">
+        <v>0.09089500000000003</v>
+      </c>
+      <c r="N37">
+        <v>0.563105</v>
+      </c>
+      <c r="O37">
+        <v>0.08446575000000008</v>
+      </c>
+      <c r="P37">
+        <v>0.4786392499999999</v>
+      </c>
+      <c r="Q37">
+        <v>-0.1753607500000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1527902096601215</v>
+      </c>
+      <c r="T37">
+        <v>1.174226123446525</v>
+      </c>
+      <c r="U37">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W37">
+        <v>0.04505</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>7.195115242862641</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1150263376464472</v>
+      </c>
+      <c r="C38">
+        <v>3.165976517575574</v>
+      </c>
+      <c r="D38">
+        <v>2.819976517575574</v>
+      </c>
+      <c r="E38">
+        <v>1.764</v>
+      </c>
+      <c r="F38">
+        <v>1.764</v>
+      </c>
+      <c r="G38">
+        <v>2.11</v>
+      </c>
+      <c r="H38">
+        <v>4.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-0.654</v>
+      </c>
+      <c r="L38">
+        <v>0.654</v>
+      </c>
+      <c r="M38">
+        <v>0.09349200000000001</v>
+      </c>
+      <c r="N38">
+        <v>0.560508</v>
+      </c>
+      <c r="O38">
+        <v>0.08407620000000007</v>
+      </c>
+      <c r="P38">
+        <v>0.4764318</v>
+      </c>
+      <c r="Q38">
+        <v>-0.1775682000000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1543880275725737</v>
+      </c>
+      <c r="T38">
+        <v>1.190685427617527</v>
+      </c>
+      <c r="U38">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W38">
+        <v>0.04505</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>6.995250930560903</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1149715390138153</v>
+      </c>
+      <c r="C39">
+        <v>3.117818396430991</v>
+      </c>
+      <c r="D39">
+        <v>2.820818396430992</v>
+      </c>
+      <c r="E39">
+        <v>1.813</v>
+      </c>
+      <c r="F39">
+        <v>1.813</v>
+      </c>
+      <c r="G39">
+        <v>2.11</v>
+      </c>
+      <c r="H39">
+        <v>4.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>-0.654</v>
+      </c>
+      <c r="L39">
+        <v>0.654</v>
+      </c>
+      <c r="M39">
+        <v>0.09608900000000002</v>
+      </c>
+      <c r="N39">
+        <v>0.557911</v>
+      </c>
+      <c r="O39">
+        <v>0.08368665000000008</v>
+      </c>
+      <c r="P39">
+        <v>0.47422435</v>
+      </c>
+      <c r="Q39">
+        <v>-0.1797756500000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.156036569863199</v>
+      </c>
+      <c r="T39">
+        <v>1.207667249381259</v>
+      </c>
+      <c r="U39">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W39">
+        <v>0.04505</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.806190094599797</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1149167403811836</v>
+      </c>
+      <c r="C40">
+        <v>3.069660778107378</v>
+      </c>
+      <c r="D40">
+        <v>2.821660778107379</v>
+      </c>
+      <c r="E40">
+        <v>1.862</v>
+      </c>
+      <c r="F40">
+        <v>1.862</v>
+      </c>
+      <c r="G40">
+        <v>2.11</v>
+      </c>
+      <c r="H40">
+        <v>4.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>-0.654</v>
+      </c>
+      <c r="L40">
+        <v>0.654</v>
+      </c>
+      <c r="M40">
+        <v>0.09868600000000001</v>
+      </c>
+      <c r="N40">
+        <v>0.555314</v>
+      </c>
+      <c r="O40">
+        <v>0.08329710000000007</v>
+      </c>
+      <c r="P40">
+        <v>0.4720168999999999</v>
+      </c>
+      <c r="Q40">
+        <v>-0.1819831000000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1577382909373929</v>
+      </c>
+      <c r="T40">
+        <v>1.225196871847047</v>
+      </c>
+      <c r="U40">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W40">
+        <v>0.04505</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.627079828952434</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1148619417485518</v>
+      </c>
+      <c r="C41">
+        <v>3.021503663055344</v>
+      </c>
+      <c r="D41">
+        <v>2.822503663055345</v>
+      </c>
+      <c r="E41">
+        <v>1.911</v>
+      </c>
+      <c r="F41">
+        <v>1.911</v>
+      </c>
+      <c r="G41">
+        <v>2.11</v>
+      </c>
+      <c r="H41">
+        <v>4.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>-0.654</v>
+      </c>
+      <c r="L41">
+        <v>0.654</v>
+      </c>
+      <c r="M41">
+        <v>0.101283</v>
+      </c>
+      <c r="N41">
+        <v>0.552717</v>
+      </c>
+      <c r="O41">
+        <v>0.08290755000000008</v>
+      </c>
+      <c r="P41">
+        <v>0.46980945</v>
+      </c>
+      <c r="Q41">
+        <v>-0.1841905500000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1594958061451668</v>
+      </c>
+      <c r="T41">
+        <v>1.243301236033024</v>
+      </c>
+      <c r="U41">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W41">
+        <v>0.04505</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.45715470513314</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.11480714311592</v>
+      </c>
+      <c r="C42">
+        <v>2.973347051726033</v>
+      </c>
+      <c r="D42">
+        <v>2.823347051726032</v>
+      </c>
+      <c r="E42">
+        <v>1.96</v>
+      </c>
+      <c r="F42">
+        <v>1.96</v>
+      </c>
+      <c r="G42">
+        <v>2.11</v>
+      </c>
+      <c r="H42">
+        <v>4.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>-0.654</v>
+      </c>
+      <c r="L42">
+        <v>0.654</v>
+      </c>
+      <c r="M42">
+        <v>0.10388</v>
+      </c>
+      <c r="N42">
+        <v>0.5501200000000001</v>
+      </c>
+      <c r="O42">
+        <v>0.08251800000000008</v>
+      </c>
+      <c r="P42">
+        <v>0.467602</v>
+      </c>
+      <c r="Q42">
+        <v>-0.1863980000000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1613119051932</v>
+      </c>
+      <c r="T42">
+        <v>1.262009079025201</v>
+      </c>
+      <c r="U42">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W42">
+        <v>0.04505</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>6.295725837504813</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1154493444832882</v>
+      </c>
+      <c r="C43">
+        <v>2.914494678604807</v>
+      </c>
+      <c r="D43">
+        <v>2.813494678604807</v>
+      </c>
+      <c r="E43">
+        <v>2.009</v>
+      </c>
+      <c r="F43">
+        <v>2.009</v>
+      </c>
+      <c r="G43">
+        <v>2.11</v>
+      </c>
+      <c r="H43">
+        <v>4.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>-0.654</v>
+      </c>
+      <c r="L43">
+        <v>0.654</v>
+      </c>
+      <c r="M43">
+        <v>0.110495</v>
+      </c>
+      <c r="N43">
+        <v>0.543505</v>
+      </c>
+      <c r="O43">
+        <v>0.08152575000000008</v>
+      </c>
+      <c r="P43">
+        <v>0.46197925</v>
+      </c>
+      <c r="Q43">
+        <v>-0.1920207500000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1631895669208275</v>
+      </c>
+      <c r="T43">
+        <v>1.281351086186604</v>
+      </c>
+      <c r="U43">
+        <v>0.055</v>
+      </c>
+      <c r="V43">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W43">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.918819856102085</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1154115458506564</v>
+      </c>
+      <c r="C44">
+        <v>2.866072663855335</v>
+      </c>
+      <c r="D44">
+        <v>2.814072663855335</v>
+      </c>
+      <c r="E44">
+        <v>2.058</v>
+      </c>
+      <c r="F44">
+        <v>2.058</v>
+      </c>
+      <c r="G44">
+        <v>2.11</v>
+      </c>
+      <c r="H44">
+        <v>4.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>-0.654</v>
+      </c>
+      <c r="L44">
+        <v>0.654</v>
+      </c>
+      <c r="M44">
+        <v>0.11319</v>
+      </c>
+      <c r="N44">
+        <v>0.54081</v>
+      </c>
+      <c r="O44">
+        <v>0.08112150000000007</v>
+      </c>
+      <c r="P44">
+        <v>0.4596884999999999</v>
+      </c>
+      <c r="Q44">
+        <v>-0.1943115000000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.16513197560458</v>
+      </c>
+      <c r="T44">
+        <v>1.301360059112194</v>
+      </c>
+      <c r="U44">
+        <v>0.055</v>
+      </c>
+      <c r="V44">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W44">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.77789557381394</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1153737472180246</v>
+      </c>
+      <c r="C45">
+        <v>2.817650886629392</v>
+      </c>
+      <c r="D45">
+        <v>2.814650886629392</v>
+      </c>
+      <c r="E45">
+        <v>2.107</v>
+      </c>
+      <c r="F45">
+        <v>2.107</v>
+      </c>
+      <c r="G45">
+        <v>2.11</v>
+      </c>
+      <c r="H45">
+        <v>4.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>-0.654</v>
+      </c>
+      <c r="L45">
+        <v>0.654</v>
+      </c>
+      <c r="M45">
+        <v>0.115885</v>
+      </c>
+      <c r="N45">
+        <v>0.538115</v>
+      </c>
+      <c r="O45">
+        <v>0.08071725000000007</v>
+      </c>
+      <c r="P45">
+        <v>0.4573977499999999</v>
+      </c>
+      <c r="Q45">
+        <v>-0.1966022500000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1671425389789906</v>
+      </c>
+      <c r="T45">
+        <v>1.322071101263242</v>
+      </c>
+      <c r="U45">
+        <v>0.055</v>
+      </c>
+      <c r="V45">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W45">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.643525909306639</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1153359485853929</v>
+      </c>
+      <c r="C46">
+        <v>2.769229347073422</v>
+      </c>
+      <c r="D46">
+        <v>2.815229347073423</v>
+      </c>
+      <c r="E46">
+        <v>2.156</v>
+      </c>
+      <c r="F46">
+        <v>2.156</v>
+      </c>
+      <c r="G46">
+        <v>2.11</v>
+      </c>
+      <c r="H46">
+        <v>4.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>-0.654</v>
+      </c>
+      <c r="L46">
+        <v>0.654</v>
+      </c>
+      <c r="M46">
+        <v>0.11858</v>
+      </c>
+      <c r="N46">
+        <v>0.53542</v>
+      </c>
+      <c r="O46">
+        <v>0.08031300000000008</v>
+      </c>
+      <c r="P46">
+        <v>0.4551069999999999</v>
+      </c>
+      <c r="Q46">
+        <v>-0.1988930000000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1692249081882015</v>
+      </c>
+      <c r="T46">
+        <v>1.343521823491115</v>
+      </c>
+      <c r="U46">
+        <v>0.055</v>
+      </c>
+      <c r="V46">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W46">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.515263956822398</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1152981499527611</v>
+      </c>
+      <c r="C47">
+        <v>2.720808045333994</v>
+      </c>
+      <c r="D47">
+        <v>2.815808045333995</v>
+      </c>
+      <c r="E47">
+        <v>2.205</v>
+      </c>
+      <c r="F47">
+        <v>2.205</v>
+      </c>
+      <c r="G47">
+        <v>2.11</v>
+      </c>
+      <c r="H47">
+        <v>4.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>-0.654</v>
+      </c>
+      <c r="L47">
+        <v>0.654</v>
+      </c>
+      <c r="M47">
+        <v>0.121275</v>
+      </c>
+      <c r="N47">
+        <v>0.532725</v>
+      </c>
+      <c r="O47">
+        <v>0.07990875000000007</v>
+      </c>
+      <c r="P47">
+        <v>0.4528162499999999</v>
+      </c>
+      <c r="Q47">
+        <v>-0.2011837500000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.171382999914111</v>
+      </c>
+      <c r="T47">
+        <v>1.365752571981818</v>
+      </c>
+      <c r="U47">
+        <v>0.055</v>
+      </c>
+      <c r="V47">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W47">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.392702535559678</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1152603513201293</v>
+      </c>
+      <c r="C48">
+        <v>2.672386981557795</v>
+      </c>
+      <c r="D48">
+        <v>2.816386981557796</v>
+      </c>
+      <c r="E48">
+        <v>2.254</v>
+      </c>
+      <c r="F48">
+        <v>2.254</v>
+      </c>
+      <c r="G48">
+        <v>2.11</v>
+      </c>
+      <c r="H48">
+        <v>4.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>-0.654</v>
+      </c>
+      <c r="L48">
+        <v>0.654</v>
+      </c>
+      <c r="M48">
+        <v>0.12397</v>
+      </c>
+      <c r="N48">
+        <v>0.53003</v>
+      </c>
+      <c r="O48">
+        <v>0.07950450000000008</v>
+      </c>
+      <c r="P48">
+        <v>0.4505254999999999</v>
+      </c>
+      <c r="Q48">
+        <v>-0.2034745000000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1736210209632024</v>
+      </c>
+      <c r="T48">
+        <v>1.388806681527733</v>
+      </c>
+      <c r="U48">
+        <v>0.055</v>
+      </c>
+      <c r="V48">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W48">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.275469871743163</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1152225526874975</v>
+      </c>
+      <c r="C49">
+        <v>2.62396615589163</v>
+      </c>
+      <c r="D49">
+        <v>2.816966155891631</v>
+      </c>
+      <c r="E49">
+        <v>2.303</v>
+      </c>
+      <c r="F49">
+        <v>2.303</v>
+      </c>
+      <c r="G49">
+        <v>2.11</v>
+      </c>
+      <c r="H49">
+        <v>4.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>-0.654</v>
+      </c>
+      <c r="L49">
+        <v>0.654</v>
+      </c>
+      <c r="M49">
+        <v>0.126665</v>
+      </c>
+      <c r="N49">
+        <v>0.527335</v>
+      </c>
+      <c r="O49">
+        <v>0.07910025000000007</v>
+      </c>
+      <c r="P49">
+        <v>0.4482347499999999</v>
+      </c>
+      <c r="Q49">
+        <v>-0.2057652500000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1759434956367877</v>
+      </c>
+      <c r="T49">
+        <v>1.412730757471607</v>
+      </c>
+      <c r="U49">
+        <v>0.055</v>
+      </c>
+      <c r="V49">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W49">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.16322583191884</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1151847540548657</v>
+      </c>
+      <c r="C50">
+        <v>2.57554556848243</v>
+      </c>
+      <c r="D50">
+        <v>2.81754556848243</v>
+      </c>
+      <c r="E50">
+        <v>2.352</v>
+      </c>
+      <c r="F50">
+        <v>2.352</v>
+      </c>
+      <c r="G50">
+        <v>2.11</v>
+      </c>
+      <c r="H50">
+        <v>4.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>-0.654</v>
+      </c>
+      <c r="L50">
+        <v>0.654</v>
+      </c>
+      <c r="M50">
+        <v>0.12936</v>
+      </c>
+      <c r="N50">
+        <v>0.52464</v>
+      </c>
+      <c r="O50">
+        <v>0.07869600000000007</v>
+      </c>
+      <c r="P50">
+        <v>0.4459439999999999</v>
+      </c>
+      <c r="Q50">
+        <v>-0.2080560000000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1783552962593571</v>
+      </c>
+      <c r="T50">
+        <v>1.437574990182553</v>
+      </c>
+      <c r="U50">
+        <v>0.055</v>
+      </c>
+      <c r="V50">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W50">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.055658627087198</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1151469554222339</v>
+      </c>
+      <c r="C51">
+        <v>2.527125219477241</v>
+      </c>
+      <c r="D51">
+        <v>2.818125219477242</v>
+      </c>
+      <c r="E51">
+        <v>2.401</v>
+      </c>
+      <c r="F51">
+        <v>2.401</v>
+      </c>
+      <c r="G51">
+        <v>2.11</v>
+      </c>
+      <c r="H51">
+        <v>4.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>-0.654</v>
+      </c>
+      <c r="L51">
+        <v>0.654</v>
+      </c>
+      <c r="M51">
+        <v>0.132055</v>
+      </c>
+      <c r="N51">
+        <v>0.521945</v>
+      </c>
+      <c r="O51">
+        <v>0.07829175000000006</v>
+      </c>
+      <c r="P51">
+        <v>0.4436532499999999</v>
+      </c>
+      <c r="Q51">
+        <v>-0.2103467500000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1808616772984979</v>
+      </c>
+      <c r="T51">
+        <v>1.463393506529223</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W51">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.95248192041195</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1151091567896021</v>
+      </c>
+      <c r="C52">
+        <v>2.478705109023235</v>
+      </c>
+      <c r="D52">
+        <v>2.818705109023236</v>
+      </c>
+      <c r="E52">
+        <v>2.45</v>
+      </c>
+      <c r="F52">
+        <v>2.45</v>
+      </c>
+      <c r="G52">
+        <v>2.11</v>
+      </c>
+      <c r="H52">
+        <v>4.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>-0.654</v>
+      </c>
+      <c r="L52">
+        <v>0.654</v>
+      </c>
+      <c r="M52">
+        <v>0.13475</v>
+      </c>
+      <c r="N52">
+        <v>0.51925</v>
+      </c>
+      <c r="O52">
+        <v>0.07788750000000007</v>
+      </c>
+      <c r="P52">
+        <v>0.4413624999999999</v>
+      </c>
+      <c r="Q52">
+        <v>-0.2126375000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1834683135792042</v>
+      </c>
+      <c r="T52">
+        <v>1.490244763529759</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W52">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.853432282003711</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1150713581569703</v>
+      </c>
+      <c r="C53">
+        <v>2.430285237267704</v>
+      </c>
+      <c r="D53">
+        <v>2.819285237267705</v>
+      </c>
+      <c r="E53">
+        <v>2.499</v>
+      </c>
+      <c r="F53">
+        <v>2.499</v>
+      </c>
+      <c r="G53">
+        <v>2.11</v>
+      </c>
+      <c r="H53">
+        <v>4.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>-0.654</v>
+      </c>
+      <c r="L53">
+        <v>0.654</v>
+      </c>
+      <c r="M53">
+        <v>0.137445</v>
+      </c>
+      <c r="N53">
+        <v>0.516555</v>
+      </c>
+      <c r="O53">
+        <v>0.07748325000000007</v>
+      </c>
+      <c r="P53">
+        <v>0.4390717499999999</v>
+      </c>
+      <c r="Q53">
+        <v>-0.2149282500000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1861813431774905</v>
+      </c>
+      <c r="T53">
+        <v>1.518191990203786</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W53">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.758266943140892</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1150335595243386</v>
+      </c>
+      <c r="C54">
+        <v>2.381865604358059</v>
+      </c>
+      <c r="D54">
+        <v>2.81986560435806</v>
+      </c>
+      <c r="E54">
+        <v>2.548</v>
+      </c>
+      <c r="F54">
+        <v>2.548</v>
+      </c>
+      <c r="G54">
+        <v>2.11</v>
+      </c>
+      <c r="H54">
+        <v>4.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>-0.654</v>
+      </c>
+      <c r="L54">
+        <v>0.654</v>
+      </c>
+      <c r="M54">
+        <v>0.14014</v>
+      </c>
+      <c r="N54">
+        <v>0.51386</v>
+      </c>
+      <c r="O54">
+        <v>0.07707900000000006</v>
+      </c>
+      <c r="P54">
+        <v>0.4367809999999999</v>
+      </c>
+      <c r="Q54">
+        <v>-0.2172190000000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1890074156757053</v>
+      </c>
+      <c r="T54">
+        <v>1.547303684655898</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W54">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.666761809618952</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1149957608917068</v>
+      </c>
+      <c r="C55">
+        <v>2.333446210441836</v>
+      </c>
+      <c r="D55">
+        <v>2.820446210441836</v>
+      </c>
+      <c r="E55">
+        <v>2.597</v>
+      </c>
+      <c r="F55">
+        <v>2.597</v>
+      </c>
+      <c r="G55">
+        <v>2.11</v>
+      </c>
+      <c r="H55">
+        <v>4.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>-0.654</v>
+      </c>
+      <c r="L55">
+        <v>0.654</v>
+      </c>
+      <c r="M55">
+        <v>0.142835</v>
+      </c>
+      <c r="N55">
+        <v>0.511165</v>
+      </c>
+      <c r="O55">
+        <v>0.07667475000000007</v>
+      </c>
+      <c r="P55">
+        <v>0.4344902499999999</v>
+      </c>
+      <c r="Q55">
+        <v>-0.2195097500000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1919537465780995</v>
+      </c>
+      <c r="T55">
+        <v>1.577654174616611</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W55">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.5787097000035</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.116702162259075</v>
+      </c>
+      <c r="C56">
+        <v>2.258471070800893</v>
+      </c>
+      <c r="D56">
+        <v>2.794471070800894</v>
+      </c>
+      <c r="E56">
+        <v>2.646</v>
+      </c>
+      <c r="F56">
+        <v>2.646</v>
+      </c>
+      <c r="G56">
+        <v>2.11</v>
+      </c>
+      <c r="H56">
+        <v>4.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>-0.654</v>
+      </c>
+      <c r="L56">
+        <v>0.654</v>
+      </c>
+      <c r="M56">
+        <v>0.1555848</v>
+      </c>
+      <c r="N56">
+        <v>0.4984152</v>
+      </c>
+      <c r="O56">
+        <v>0.07476228000000007</v>
+      </c>
+      <c r="P56">
+        <v>0.4236529199999999</v>
+      </c>
+      <c r="Q56">
+        <v>-0.2303470800000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.195028178824076</v>
+      </c>
+      <c r="T56">
+        <v>1.609324251097354</v>
+      </c>
+      <c r="U56">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W56">
+        <v>0.04998</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.203495457139772</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1166966636264432</v>
+      </c>
+      <c r="C57">
+        <v>2.209554003555485</v>
+      </c>
+      <c r="D57">
+        <v>2.794554003555485</v>
+      </c>
+      <c r="E57">
+        <v>2.695</v>
+      </c>
+      <c r="F57">
+        <v>2.695</v>
+      </c>
+      <c r="G57">
+        <v>2.11</v>
+      </c>
+      <c r="H57">
+        <v>4.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>-0.654</v>
+      </c>
+      <c r="L57">
+        <v>0.654</v>
+      </c>
+      <c r="M57">
+        <v>0.158466</v>
+      </c>
+      <c r="N57">
+        <v>0.495534</v>
+      </c>
+      <c r="O57">
+        <v>0.07433010000000007</v>
+      </c>
+      <c r="P57">
+        <v>0.4212039</v>
+      </c>
+      <c r="Q57">
+        <v>-0.2327961000000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1982392525032071</v>
+      </c>
+      <c r="T57">
+        <v>1.642401886532797</v>
+      </c>
+      <c r="U57">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W57">
+        <v>0.04998</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.127068267009958</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1166911649938114</v>
+      </c>
+      <c r="C58">
+        <v>2.160636941232686</v>
+      </c>
+      <c r="D58">
+        <v>2.794636941232687</v>
+      </c>
+      <c r="E58">
+        <v>2.744000000000001</v>
+      </c>
+      <c r="F58">
+        <v>2.744000000000001</v>
+      </c>
+      <c r="G58">
+        <v>2.11</v>
+      </c>
+      <c r="H58">
+        <v>4.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>-0.654</v>
+      </c>
+      <c r="L58">
+        <v>0.654</v>
+      </c>
+      <c r="M58">
+        <v>0.1613472000000001</v>
+      </c>
+      <c r="N58">
+        <v>0.4926528</v>
+      </c>
+      <c r="O58">
+        <v>0.07389792000000006</v>
+      </c>
+      <c r="P58">
+        <v>0.4187548799999999</v>
+      </c>
+      <c r="Q58">
+        <v>-0.2352451200000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2015962840768441</v>
+      </c>
+      <c r="T58">
+        <v>1.67698305085167</v>
+      </c>
+      <c r="U58">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W58">
+        <v>0.04998</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.053370619384779</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1187205663611796</v>
+      </c>
+      <c r="C59">
+        <v>2.081357572005491</v>
+      </c>
+      <c r="D59">
+        <v>2.764357572005491</v>
+      </c>
+      <c r="E59">
+        <v>2.793000000000001</v>
+      </c>
+      <c r="F59">
+        <v>2.793000000000001</v>
+      </c>
+      <c r="G59">
+        <v>2.11</v>
+      </c>
+      <c r="H59">
+        <v>4.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>-0.654</v>
+      </c>
+      <c r="L59">
+        <v>0.654</v>
+      </c>
+      <c r="M59">
+        <v>0.175959</v>
+      </c>
+      <c r="N59">
+        <v>0.478041</v>
+      </c>
+      <c r="O59">
+        <v>0.07170615000000007</v>
+      </c>
+      <c r="P59">
+        <v>0.4063348499999999</v>
+      </c>
+      <c r="Q59">
+        <v>-0.2476651500000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2051094566539061</v>
+      </c>
+      <c r="T59">
+        <v>1.713172641417932</v>
+      </c>
+      <c r="U59">
+        <v>0.063</v>
+      </c>
+      <c r="V59">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W59">
+        <v>0.05354999999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.716774930523588</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1187507677285478</v>
+      </c>
+      <c r="C60">
+        <v>2.031911911361775</v>
+      </c>
+      <c r="D60">
+        <v>2.763911911361775</v>
+      </c>
+      <c r="E60">
+        <v>2.842</v>
+      </c>
+      <c r="F60">
+        <v>2.842</v>
+      </c>
+      <c r="G60">
+        <v>2.11</v>
+      </c>
+      <c r="H60">
+        <v>4.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>-0.654</v>
+      </c>
+      <c r="L60">
+        <v>0.654</v>
+      </c>
+      <c r="M60">
+        <v>0.179046</v>
+      </c>
+      <c r="N60">
+        <v>0.474954</v>
+      </c>
+      <c r="O60">
+        <v>0.07124310000000006</v>
+      </c>
+      <c r="P60">
+        <v>0.4037108999999999</v>
+      </c>
+      <c r="Q60">
+        <v>-0.2502891000000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2087899231632091</v>
+      </c>
+      <c r="T60">
+        <v>1.751085545820681</v>
+      </c>
+      <c r="U60">
+        <v>0.063</v>
+      </c>
+      <c r="V60">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W60">
+        <v>0.05354999999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.65269260413525</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.118780969095916</v>
+      </c>
+      <c r="C61">
+        <v>1.982466394390784</v>
+      </c>
+      <c r="D61">
+        <v>2.763466394390784</v>
+      </c>
+      <c r="E61">
+        <v>2.891</v>
+      </c>
+      <c r="F61">
+        <v>2.891</v>
+      </c>
+      <c r="G61">
+        <v>2.11</v>
+      </c>
+      <c r="H61">
+        <v>4.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>-0.654</v>
+      </c>
+      <c r="L61">
+        <v>0.654</v>
+      </c>
+      <c r="M61">
+        <v>0.182133</v>
+      </c>
+      <c r="N61">
+        <v>0.471867</v>
+      </c>
+      <c r="O61">
+        <v>0.07078005000000007</v>
+      </c>
+      <c r="P61">
+        <v>0.4010869499999999</v>
+      </c>
+      <c r="Q61">
+        <v>-0.2529130500000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2126499246241854</v>
+      </c>
+      <c r="T61">
+        <v>1.790847860194298</v>
+      </c>
+      <c r="U61">
+        <v>0.063</v>
+      </c>
+      <c r="V61">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W61">
+        <v>0.05354999999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.590782559997365</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1188111704632842</v>
+      </c>
+      <c r="C62">
+        <v>1.933021021023056</v>
+      </c>
+      <c r="D62">
+        <v>2.763021021023056</v>
+      </c>
+      <c r="E62">
+        <v>2.94</v>
+      </c>
+      <c r="F62">
+        <v>2.94</v>
+      </c>
+      <c r="G62">
+        <v>2.11</v>
+      </c>
+      <c r="H62">
+        <v>4.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>-0.654</v>
+      </c>
+      <c r="L62">
+        <v>0.654</v>
+      </c>
+      <c r="M62">
+        <v>0.18522</v>
+      </c>
+      <c r="N62">
+        <v>0.46878</v>
+      </c>
+      <c r="O62">
+        <v>0.07031700000000007</v>
+      </c>
+      <c r="P62">
+        <v>0.398463</v>
+      </c>
+      <c r="Q62">
+        <v>-0.2555370000000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2167029261582106</v>
+      </c>
+      <c r="T62">
+        <v>1.832598290286595</v>
+      </c>
+      <c r="U62">
+        <v>0.063</v>
+      </c>
+      <c r="V62">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W62">
+        <v>0.05354999999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.530936183997408</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1225227218306525</v>
+      </c>
+      <c r="C63">
+        <v>1.830359187213503</v>
+      </c>
+      <c r="D63">
+        <v>2.709359187213503</v>
+      </c>
+      <c r="E63">
+        <v>2.989</v>
+      </c>
+      <c r="F63">
+        <v>2.989</v>
+      </c>
+      <c r="G63">
+        <v>2.11</v>
+      </c>
+      <c r="H63">
+        <v>4.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>-0.654</v>
+      </c>
+      <c r="L63">
+        <v>0.654</v>
+      </c>
+      <c r="M63">
+        <v>0.2095289</v>
+      </c>
+      <c r="N63">
+        <v>0.4444711</v>
+      </c>
+      <c r="O63">
+        <v>0.06667066500000006</v>
+      </c>
+      <c r="P63">
+        <v>0.3778004349999999</v>
+      </c>
+      <c r="Q63">
+        <v>-0.2761995650000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2209637739247499</v>
+      </c>
+      <c r="T63">
+        <v>1.876489768075933</v>
+      </c>
+      <c r="U63">
+        <v>0.0701</v>
+      </c>
+      <c r="V63">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W63">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.121287803257689</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1226132731980207</v>
+      </c>
+      <c r="C64">
+        <v>1.780076024561712</v>
+      </c>
+      <c r="D64">
+        <v>2.708076024561712</v>
+      </c>
+      <c r="E64">
+        <v>3.038</v>
+      </c>
+      <c r="F64">
+        <v>3.038</v>
+      </c>
+      <c r="G64">
+        <v>2.11</v>
+      </c>
+      <c r="H64">
+        <v>4.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>-0.654</v>
+      </c>
+      <c r="L64">
+        <v>0.654</v>
+      </c>
+      <c r="M64">
+        <v>0.2129638</v>
+      </c>
+      <c r="N64">
+        <v>0.4410362</v>
+      </c>
+      <c r="O64">
+        <v>0.06615543000000006</v>
+      </c>
+      <c r="P64">
+        <v>0.3748807699999999</v>
+      </c>
+      <c r="Q64">
+        <v>-0.2791192300000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2254488768368965</v>
+      </c>
+      <c r="T64">
+        <v>1.922691323643658</v>
+      </c>
+      <c r="U64">
+        <v>0.0701</v>
+      </c>
+      <c r="V64">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W64">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.070944451592242</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1227038245653889</v>
+      </c>
+      <c r="C65">
+        <v>1.729794076755835</v>
+      </c>
+      <c r="D65">
+        <v>2.706794076755835</v>
+      </c>
+      <c r="E65">
+        <v>3.087</v>
+      </c>
+      <c r="F65">
+        <v>3.087</v>
+      </c>
+      <c r="G65">
+        <v>2.11</v>
+      </c>
+      <c r="H65">
+        <v>4.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>-0.654</v>
+      </c>
+      <c r="L65">
+        <v>0.654</v>
+      </c>
+      <c r="M65">
+        <v>0.2163987</v>
+      </c>
+      <c r="N65">
+        <v>0.4376013</v>
+      </c>
+      <c r="O65">
+        <v>0.06564019500000007</v>
+      </c>
+      <c r="P65">
+        <v>0.371961105</v>
+      </c>
+      <c r="Q65">
+        <v>-0.2820388950000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2301764177442943</v>
+      </c>
+      <c r="T65">
+        <v>1.971390260593421</v>
+      </c>
+      <c r="U65">
+        <v>0.0701</v>
+      </c>
+      <c r="V65">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W65">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.022199301566969</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1343815759327571</v>
+      </c>
+      <c r="C66">
+        <v>1.525056375894509</v>
+      </c>
+      <c r="D66">
+        <v>2.551056375894509</v>
+      </c>
+      <c r="E66">
+        <v>3.136</v>
+      </c>
+      <c r="F66">
+        <v>3.136</v>
+      </c>
+      <c r="G66">
+        <v>2.11</v>
+      </c>
+      <c r="H66">
+        <v>4.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>-0.654</v>
+      </c>
+      <c r="L66">
+        <v>0.654</v>
+      </c>
+      <c r="M66">
+        <v>0.2866304000000001</v>
+      </c>
+      <c r="N66">
+        <v>0.3673696</v>
+      </c>
+      <c r="O66">
+        <v>0.05510544000000004</v>
+      </c>
+      <c r="P66">
+        <v>0.3122641599999999</v>
+      </c>
+      <c r="Q66">
+        <v>-0.3417358400000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2351665998132142</v>
+      </c>
+      <c r="T66">
+        <v>2.022794694040393</v>
+      </c>
+      <c r="U66">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V66">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W66">
+        <v>0.07769</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.28168400839548</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1346531773001253</v>
+      </c>
+      <c r="C67">
+        <v>1.472647191011206</v>
+      </c>
+      <c r="D67">
+        <v>2.547647191011207</v>
+      </c>
+      <c r="E67">
+        <v>3.185</v>
+      </c>
+      <c r="F67">
+        <v>3.185</v>
+      </c>
+      <c r="G67">
+        <v>2.11</v>
+      </c>
+      <c r="H67">
+        <v>4.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>-0.654</v>
+      </c>
+      <c r="L67">
+        <v>0.654</v>
+      </c>
+      <c r="M67">
+        <v>0.2911090000000001</v>
+      </c>
+      <c r="N67">
+        <v>0.362891</v>
+      </c>
+      <c r="O67">
+        <v>0.05443365000000004</v>
+      </c>
+      <c r="P67">
+        <v>0.3084573499999999</v>
+      </c>
+      <c r="Q67">
+        <v>-0.3455426500000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2404419351432152</v>
+      </c>
+      <c r="T67">
+        <v>2.077136523684335</v>
+      </c>
+      <c r="U67">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W67">
+        <v>0.07769</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.246581177497088</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1349247786674935</v>
+      </c>
+      <c r="C68">
+        <v>1.420247105911238</v>
+      </c>
+      <c r="D68">
+        <v>2.544247105911239</v>
+      </c>
+      <c r="E68">
+        <v>3.234</v>
+      </c>
+      <c r="F68">
+        <v>3.234</v>
+      </c>
+      <c r="G68">
+        <v>2.11</v>
+      </c>
+      <c r="H68">
+        <v>4.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>-0.654</v>
+      </c>
+      <c r="L68">
+        <v>0.654</v>
+      </c>
+      <c r="M68">
+        <v>0.2955876000000001</v>
+      </c>
+      <c r="N68">
+        <v>0.3584124</v>
+      </c>
+      <c r="O68">
+        <v>0.05376186000000004</v>
+      </c>
+      <c r="P68">
+        <v>0.3046505399999999</v>
+      </c>
+      <c r="Q68">
+        <v>-0.3493494600000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2460275843161575</v>
+      </c>
+      <c r="T68">
+        <v>2.134674931542627</v>
+      </c>
+      <c r="U68">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W68">
+        <v>0.07769</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.212542068747132</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1351963800348617</v>
+      </c>
+      <c r="C69">
+        <v>1.367856084209503</v>
+      </c>
+      <c r="D69">
+        <v>2.540856084209504</v>
+      </c>
+      <c r="E69">
+        <v>3.283</v>
+      </c>
+      <c r="F69">
+        <v>3.283</v>
+      </c>
+      <c r="G69">
+        <v>2.11</v>
+      </c>
+      <c r="H69">
+        <v>4.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>-0.654</v>
+      </c>
+      <c r="L69">
+        <v>0.654</v>
+      </c>
+      <c r="M69">
+        <v>0.3000662000000001</v>
+      </c>
+      <c r="N69">
+        <v>0.3539338</v>
+      </c>
+      <c r="O69">
+        <v>0.05309007000000004</v>
+      </c>
+      <c r="P69">
+        <v>0.3008437299999999</v>
+      </c>
+      <c r="Q69">
+        <v>-0.3531562700000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2519517576813992</v>
+      </c>
+      <c r="T69">
+        <v>2.195700515634755</v>
+      </c>
+      <c r="U69">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W69">
+        <v>0.07769</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.179519052795682</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.13546798140223</v>
+      </c>
+      <c r="C70">
+        <v>1.31547408971462</v>
+      </c>
+      <c r="D70">
+        <v>2.537474089714621</v>
+      </c>
+      <c r="E70">
+        <v>3.332</v>
+      </c>
+      <c r="F70">
+        <v>3.332</v>
+      </c>
+      <c r="G70">
+        <v>2.11</v>
+      </c>
+      <c r="H70">
+        <v>4.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>-0.654</v>
+      </c>
+      <c r="L70">
+        <v>0.654</v>
+      </c>
+      <c r="M70">
+        <v>0.3045448000000001</v>
+      </c>
+      <c r="N70">
+        <v>0.3494552</v>
+      </c>
+      <c r="O70">
+        <v>0.05241828000000004</v>
+      </c>
+      <c r="P70">
+        <v>0.2970369199999999</v>
+      </c>
+      <c r="Q70">
+        <v>-0.3569630800000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2582461918819686</v>
+      </c>
+      <c r="T70">
+        <v>2.260540198732641</v>
+      </c>
+      <c r="U70">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W70">
+        <v>0.07769</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.147467302019276</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1357395827695982</v>
+      </c>
+      <c r="C71">
+        <v>1.263101086427642</v>
+      </c>
+      <c r="D71">
+        <v>2.534101086427643</v>
+      </c>
+      <c r="E71">
+        <v>3.381000000000001</v>
+      </c>
+      <c r="F71">
+        <v>3.381000000000001</v>
+      </c>
+      <c r="G71">
+        <v>2.11</v>
+      </c>
+      <c r="H71">
+        <v>4.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>-0.654</v>
+      </c>
+      <c r="L71">
+        <v>0.654</v>
+      </c>
+      <c r="M71">
+        <v>0.3090234000000001</v>
+      </c>
+      <c r="N71">
+        <v>0.3449765999999999</v>
+      </c>
+      <c r="O71">
+        <v>0.05174649000000003</v>
+      </c>
+      <c r="P71">
+        <v>0.2932301099999999</v>
+      </c>
+      <c r="Q71">
+        <v>-0.3607698900000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2649467186116071</v>
+      </c>
+      <c r="T71">
+        <v>2.329563087191681</v>
+      </c>
+      <c r="U71">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W71">
+        <v>0.07769</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.116344587497257</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1360111841369664</v>
+      </c>
+      <c r="C72">
+        <v>1.21073703854078</v>
+      </c>
+      <c r="D72">
+        <v>2.530737038540781</v>
+      </c>
+      <c r="E72">
+        <v>3.430000000000001</v>
+      </c>
+      <c r="F72">
+        <v>3.430000000000001</v>
+      </c>
+      <c r="G72">
+        <v>2.11</v>
+      </c>
+      <c r="H72">
+        <v>4.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>-0.654</v>
+      </c>
+      <c r="L72">
+        <v>0.654</v>
+      </c>
+      <c r="M72">
+        <v>0.3135020000000001</v>
+      </c>
+      <c r="N72">
+        <v>0.340498</v>
+      </c>
+      <c r="O72">
+        <v>0.05107470000000004</v>
+      </c>
+      <c r="P72">
+        <v>0.2894232999999999</v>
+      </c>
+      <c r="Q72">
+        <v>-0.3645767000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2720939471232213</v>
+      </c>
+      <c r="T72">
+        <v>2.40318750154799</v>
+      </c>
+      <c r="U72">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W72">
+        <v>0.07769</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.086111093390153</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1362827855043346</v>
+      </c>
+      <c r="C73">
+        <v>1.158381910436131</v>
+      </c>
+      <c r="D73">
+        <v>2.527381910436131</v>
+      </c>
+      <c r="E73">
+        <v>3.479</v>
+      </c>
+      <c r="F73">
+        <v>3.479</v>
+      </c>
+      <c r="G73">
+        <v>2.11</v>
+      </c>
+      <c r="H73">
+        <v>4.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>-0.654</v>
+      </c>
+      <c r="L73">
+        <v>0.654</v>
+      </c>
+      <c r="M73">
+        <v>0.3179806000000001</v>
+      </c>
+      <c r="N73">
+        <v>0.3360194</v>
+      </c>
+      <c r="O73">
+        <v>0.05040291000000004</v>
+      </c>
+      <c r="P73">
+        <v>0.2856164899999999</v>
+      </c>
+      <c r="Q73">
+        <v>-0.3683835100000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2797340879459813</v>
+      </c>
+      <c r="T73">
+        <v>2.481889461721974</v>
+      </c>
+      <c r="U73">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W73">
+        <v>0.07769</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.056729247004377</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1365543868717028</v>
+      </c>
+      <c r="C74">
+        <v>1.106035666684424</v>
+      </c>
+      <c r="D74">
+        <v>2.524035666684424</v>
+      </c>
+      <c r="E74">
+        <v>3.528</v>
+      </c>
+      <c r="F74">
+        <v>3.528</v>
+      </c>
+      <c r="G74">
+        <v>2.11</v>
+      </c>
+      <c r="H74">
+        <v>4.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>-0.654</v>
+      </c>
+      <c r="L74">
+        <v>0.654</v>
+      </c>
+      <c r="M74">
+        <v>0.3224592000000001</v>
+      </c>
+      <c r="N74">
+        <v>0.3315408</v>
+      </c>
+      <c r="O74">
+        <v>0.04973112000000004</v>
+      </c>
+      <c r="P74">
+        <v>0.28180968</v>
+      </c>
+      <c r="Q74">
+        <v>-0.3721903200000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2879199531132243</v>
+      </c>
+      <c r="T74">
+        <v>2.566212990479816</v>
+      </c>
+      <c r="U74">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W74">
+        <v>0.07769</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.028163563018205</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.136825988239071</v>
+      </c>
+      <c r="C75">
+        <v>1.053698272043773</v>
+      </c>
+      <c r="D75">
+        <v>2.520698272043774</v>
+      </c>
+      <c r="E75">
+        <v>3.577</v>
+      </c>
+      <c r="F75">
+        <v>3.577</v>
+      </c>
+      <c r="G75">
+        <v>2.11</v>
+      </c>
+      <c r="H75">
+        <v>4.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>-0.654</v>
+      </c>
+      <c r="L75">
+        <v>0.654</v>
+      </c>
+      <c r="M75">
+        <v>0.3269378</v>
+      </c>
+      <c r="N75">
+        <v>0.3270622</v>
+      </c>
+      <c r="O75">
+        <v>0.04905933000000005</v>
+      </c>
+      <c r="P75">
+        <v>0.27800287</v>
+      </c>
+      <c r="Q75">
+        <v>-0.3759971300000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.296712178663226</v>
+      </c>
+      <c r="T75">
+        <v>2.656782706553053</v>
+      </c>
+      <c r="U75">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W75">
+        <v>0.07769</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.000380500511106</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1503694896064392</v>
+      </c>
+      <c r="C76">
+        <v>0.848778379562396</v>
+      </c>
+      <c r="D76">
+        <v>2.364778379562397</v>
+      </c>
+      <c r="E76">
+        <v>3.626</v>
+      </c>
+      <c r="F76">
+        <v>3.626</v>
+      </c>
+      <c r="G76">
+        <v>2.11</v>
+      </c>
+      <c r="H76">
+        <v>4.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>-0.654</v>
+      </c>
+      <c r="L76">
+        <v>0.654</v>
+      </c>
+      <c r="M76">
+        <v>0.407925</v>
+      </c>
+      <c r="N76">
+        <v>0.246075</v>
+      </c>
+      <c r="O76">
+        <v>0.03691125000000003</v>
+      </c>
+      <c r="P76">
+        <v>0.20916375</v>
+      </c>
+      <c r="Q76">
+        <v>-0.44483625</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3061807292555355</v>
+      </c>
+      <c r="T76">
+        <v>2.754319323862693</v>
+      </c>
+      <c r="U76">
+        <v>0.1125</v>
+      </c>
+      <c r="V76">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W76">
+        <v>0.09562499999999999</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>1.603235888950175</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1508204409738074</v>
+      </c>
+      <c r="C77">
+        <v>0.7949179314034738</v>
+      </c>
+      <c r="D77">
+        <v>2.359917931403475</v>
+      </c>
+      <c r="E77">
+        <v>3.675</v>
+      </c>
+      <c r="F77">
+        <v>3.675</v>
+      </c>
+      <c r="G77">
+        <v>2.11</v>
+      </c>
+      <c r="H77">
+        <v>4.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>-0.654</v>
+      </c>
+      <c r="L77">
+        <v>0.654</v>
+      </c>
+      <c r="M77">
+        <v>0.4134375</v>
+      </c>
+      <c r="N77">
+        <v>0.2405625</v>
+      </c>
+      <c r="O77">
+        <v>0.03608437500000004</v>
+      </c>
+      <c r="P77">
+        <v>0.204478125</v>
+      </c>
+      <c r="Q77">
+        <v>-0.4495218750000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3164067638952298</v>
+      </c>
+      <c r="T77">
+        <v>2.859658870557105</v>
+      </c>
+      <c r="U77">
+        <v>0.1125</v>
+      </c>
+      <c r="V77">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W77">
+        <v>0.09562499999999999</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>1.581859410430839</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1512713923411756</v>
+      </c>
+      <c r="C78">
+        <v>0.7410774221112089</v>
+      </c>
+      <c r="D78">
+        <v>2.355077422111209</v>
+      </c>
+      <c r="E78">
+        <v>3.724</v>
+      </c>
+      <c r="F78">
+        <v>3.724</v>
+      </c>
+      <c r="G78">
+        <v>2.11</v>
+      </c>
+      <c r="H78">
+        <v>4.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>-0.654</v>
+      </c>
+      <c r="L78">
+        <v>0.654</v>
+      </c>
+      <c r="M78">
+        <v>0.41895</v>
+      </c>
+      <c r="N78">
+        <v>0.23505</v>
+      </c>
+      <c r="O78">
+        <v>0.03525750000000003</v>
+      </c>
+      <c r="P78">
+        <v>0.1997925</v>
+      </c>
+      <c r="Q78">
+        <v>-0.4542075000000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3274849680882319</v>
+      </c>
+      <c r="T78">
+        <v>2.973776712809383</v>
+      </c>
+      <c r="U78">
+        <v>0.1125</v>
+      </c>
+      <c r="V78">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W78">
+        <v>0.09562499999999999</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>1.561045470819907</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1517223437085439</v>
+      </c>
+      <c r="C79">
+        <v>0.6872567292448446</v>
+      </c>
+      <c r="D79">
+        <v>2.350256729244846</v>
+      </c>
+      <c r="E79">
+        <v>3.773000000000001</v>
+      </c>
+      <c r="F79">
+        <v>3.773000000000001</v>
+      </c>
+      <c r="G79">
+        <v>2.11</v>
+      </c>
+      <c r="H79">
+        <v>4.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>-0.654</v>
+      </c>
+      <c r="L79">
+        <v>0.654</v>
+      </c>
+      <c r="M79">
+        <v>0.4244625000000001</v>
+      </c>
+      <c r="N79">
+        <v>0.2295374999999999</v>
+      </c>
+      <c r="O79">
+        <v>0.03443062500000002</v>
+      </c>
+      <c r="P79">
+        <v>0.1951068749999999</v>
+      </c>
+      <c r="Q79">
+        <v>-0.4588931250000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3395264943849733</v>
+      </c>
+      <c r="T79">
+        <v>3.097817845692295</v>
+      </c>
+      <c r="U79">
+        <v>0.1125</v>
+      </c>
+      <c r="V79">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W79">
+        <v>0.09562499999999999</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>1.540772153017051</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1521732950759121</v>
+      </c>
+      <c r="C80">
+        <v>0.6334557313640956</v>
+      </c>
+      <c r="D80">
+        <v>2.345455731364096</v>
+      </c>
+      <c r="E80">
+        <v>3.822000000000001</v>
+      </c>
+      <c r="F80">
+        <v>3.822000000000001</v>
+      </c>
+      <c r="G80">
+        <v>2.11</v>
+      </c>
+      <c r="H80">
+        <v>4.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>-0.654</v>
+      </c>
+      <c r="L80">
+        <v>0.654</v>
+      </c>
+      <c r="M80">
+        <v>0.4299750000000001</v>
+      </c>
+      <c r="N80">
+        <v>0.224025</v>
+      </c>
+      <c r="O80">
+        <v>0.03360375000000003</v>
+      </c>
+      <c r="P80">
+        <v>0.1904212499999999</v>
+      </c>
+      <c r="Q80">
+        <v>-0.4635787500000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3526627048905095</v>
+      </c>
+      <c r="T80">
+        <v>3.233135445200927</v>
+      </c>
+      <c r="U80">
+        <v>0.1125</v>
+      </c>
+      <c r="V80">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W80">
+        <v>0.09562499999999999</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>1.521018663875807</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1526242464432803</v>
+      </c>
+      <c r="C81">
+        <v>0.5796743080189382</v>
+      </c>
+      <c r="D81">
+        <v>2.340674308018939</v>
+      </c>
+      <c r="E81">
+        <v>3.871</v>
+      </c>
+      <c r="F81">
+        <v>3.871</v>
+      </c>
+      <c r="G81">
+        <v>2.11</v>
+      </c>
+      <c r="H81">
+        <v>4.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>-0.654</v>
+      </c>
+      <c r="L81">
+        <v>0.654</v>
+      </c>
+      <c r="M81">
+        <v>0.4354875000000001</v>
+      </c>
+      <c r="N81">
+        <v>0.2185124999999999</v>
+      </c>
+      <c r="O81">
+        <v>0.03277687500000002</v>
+      </c>
+      <c r="P81">
+        <v>0.1857356249999999</v>
+      </c>
+      <c r="Q81">
+        <v>-0.4682643750000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3670499830632395</v>
+      </c>
+      <c r="T81">
+        <v>3.381340435138951</v>
+      </c>
+      <c r="U81">
+        <v>0.1125</v>
+      </c>
+      <c r="V81">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W81">
+        <v>0.09562499999999999</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>1.501765263067252</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2152554164319469</v>
+      </c>
+      <c r="C82">
+        <v>0.01418655843148775</v>
+      </c>
+      <c r="D82">
+        <v>1.824186558431488</v>
+      </c>
+      <c r="E82">
+        <v>3.92</v>
+      </c>
+      <c r="F82">
+        <v>3.92</v>
+      </c>
+      <c r="G82">
+        <v>2.11</v>
+      </c>
+      <c r="H82">
+        <v>4.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>-0.654</v>
+      </c>
+      <c r="L82">
+        <v>0.654</v>
+      </c>
+      <c r="M82">
+        <v>0.770672</v>
+      </c>
+      <c r="N82">
+        <v>-0.116672</v>
+      </c>
+      <c r="O82">
+        <v>-0.01750080000000001</v>
+      </c>
+      <c r="P82">
+        <v>-0.09917119999999999</v>
+      </c>
+      <c r="Q82">
+        <v>-0.7531712</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3899791229760611</v>
+      </c>
+      <c r="T82">
+        <v>3.617536115049298</v>
+      </c>
+      <c r="U82">
+        <v>0.1966</v>
+      </c>
+      <c r="V82">
+        <v>0.1272915066331722</v>
+      </c>
+      <c r="W82">
+        <v>0.1715744897959183</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.8486100442211473</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2168334164319469</v>
+      </c>
+      <c r="C83">
+        <v>-0.04489893127023326</v>
+      </c>
+      <c r="D83">
+        <v>1.814101068729768</v>
+      </c>
+      <c r="E83">
+        <v>3.969000000000001</v>
+      </c>
+      <c r="F83">
+        <v>3.969000000000001</v>
+      </c>
+      <c r="G83">
+        <v>2.11</v>
+      </c>
+      <c r="H83">
+        <v>4.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>-0.654</v>
+      </c>
+      <c r="L83">
+        <v>0.654</v>
+      </c>
+      <c r="M83">
+        <v>0.7803054000000001</v>
+      </c>
+      <c r="N83">
+        <v>-0.1263054000000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.01894581000000004</v>
+      </c>
+      <c r="P83">
+        <v>-0.1073595900000001</v>
+      </c>
+      <c r="Q83">
+        <v>-0.7613595900000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4084622347116432</v>
+      </c>
+      <c r="T83">
+        <v>3.807932752683472</v>
+      </c>
+      <c r="U83">
+        <v>0.1966</v>
+      </c>
+      <c r="V83">
+        <v>0.1257200065512812</v>
+      </c>
+      <c r="W83">
+        <v>0.1718834467120181</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.8381333770085404</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2184114164319469</v>
+      </c>
+      <c r="C84">
+        <v>-0.1038735136475712</v>
+      </c>
+      <c r="D84">
+        <v>1.80412648635243</v>
+      </c>
+      <c r="E84">
+        <v>4.018000000000001</v>
+      </c>
+      <c r="F84">
+        <v>4.018000000000001</v>
+      </c>
+      <c r="G84">
+        <v>2.11</v>
+      </c>
+      <c r="H84">
+        <v>4.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>-0.654</v>
+      </c>
+      <c r="L84">
+        <v>0.654</v>
+      </c>
+      <c r="M84">
+        <v>0.7899388000000002</v>
+      </c>
+      <c r="N84">
+        <v>-0.1359388000000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.02039082000000004</v>
+      </c>
+      <c r="P84">
+        <v>-0.1155479800000001</v>
+      </c>
+      <c r="Q84">
+        <v>-0.7695479800000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4289990255289568</v>
+      </c>
+      <c r="T84">
+        <v>4.019484572276999</v>
+      </c>
+      <c r="U84">
+        <v>0.1966</v>
+      </c>
+      <c r="V84">
+        <v>0.1241868357396802</v>
+      </c>
+      <c r="W84">
+        <v>0.1721848680935789</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.8279122382645338</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2199894164319469</v>
+      </c>
+      <c r="C85">
+        <v>-0.1627390081221773</v>
+      </c>
+      <c r="D85">
+        <v>1.794260991877824</v>
+      </c>
+      <c r="E85">
+        <v>4.067000000000001</v>
+      </c>
+      <c r="F85">
+        <v>4.067000000000001</v>
+      </c>
+      <c r="G85">
+        <v>2.11</v>
+      </c>
+      <c r="H85">
+        <v>4.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>-0.654</v>
+      </c>
+      <c r="L85">
+        <v>0.654</v>
+      </c>
+      <c r="M85">
+        <v>0.7995722000000002</v>
+      </c>
+      <c r="N85">
+        <v>-0.1455722000000002</v>
+      </c>
+      <c r="O85">
+        <v>-0.02183583000000004</v>
+      </c>
+      <c r="P85">
+        <v>-0.1237363700000001</v>
+      </c>
+      <c r="Q85">
+        <v>-0.7777363700000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4519519093836014</v>
+      </c>
+      <c r="T85">
+        <v>4.25592484123447</v>
+      </c>
+      <c r="U85">
+        <v>0.1966</v>
+      </c>
+      <c r="V85">
+        <v>0.1226906088030575</v>
+      </c>
+      <c r="W85">
+        <v>0.1724790263093189</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.8179373920203827</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2215674164319469</v>
+      </c>
+      <c r="C86">
+        <v>-0.2214971945356039</v>
+      </c>
+      <c r="D86">
+        <v>1.784502805464397</v>
+      </c>
+      <c r="E86">
+        <v>4.116000000000001</v>
+      </c>
+      <c r="F86">
+        <v>4.116000000000001</v>
+      </c>
+      <c r="G86">
+        <v>2.11</v>
+      </c>
+      <c r="H86">
+        <v>4.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>-0.654</v>
+      </c>
+      <c r="L86">
+        <v>0.654</v>
+      </c>
+      <c r="M86">
+        <v>0.8092056000000001</v>
+      </c>
+      <c r="N86">
+        <v>-0.1552056000000001</v>
+      </c>
+      <c r="O86">
+        <v>-0.02328084000000003</v>
+      </c>
+      <c r="P86">
+        <v>-0.13192476</v>
+      </c>
+      <c r="Q86">
+        <v>-0.7859247600000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4777739037200762</v>
+      </c>
+      <c r="T86">
+        <v>4.521920143811621</v>
+      </c>
+      <c r="U86">
+        <v>0.1966</v>
+      </c>
+      <c r="V86">
+        <v>0.1212300063173069</v>
+      </c>
+      <c r="W86">
+        <v>0.1727661807580175</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.8082000421153783</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2384060531850191</v>
+      </c>
+      <c r="C87">
+        <v>-0.3683787776604541</v>
+      </c>
+      <c r="D87">
+        <v>1.686621222339546</v>
+      </c>
+      <c r="E87">
+        <v>4.165</v>
+      </c>
+      <c r="F87">
+        <v>4.165</v>
+      </c>
+      <c r="G87">
+        <v>2.11</v>
+      </c>
+      <c r="H87">
+        <v>4.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>-0.654</v>
+      </c>
+      <c r="L87">
+        <v>0.654</v>
+      </c>
+      <c r="M87">
+        <v>0.890477</v>
+      </c>
+      <c r="N87">
+        <v>-0.2364769999999999</v>
+      </c>
+      <c r="O87">
+        <v>-0.03547155000000003</v>
+      </c>
+      <c r="P87">
+        <v>-0.2010054499999999</v>
+      </c>
+      <c r="Q87">
+        <v>-0.8550054499999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5113097423218962</v>
+      </c>
+      <c r="T87">
+        <v>4.867376634113348</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.1101656752504558</v>
+      </c>
+      <c r="W87">
+        <v>0.1902465786314526</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.7344378350030378</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2401560531850191</v>
+      </c>
+      <c r="C88">
+        <v>-0.4269389066930582</v>
+      </c>
+      <c r="D88">
+        <v>1.677061093306942</v>
+      </c>
+      <c r="E88">
+        <v>4.214</v>
+      </c>
+      <c r="F88">
+        <v>4.214</v>
+      </c>
+      <c r="G88">
+        <v>2.11</v>
+      </c>
+      <c r="H88">
+        <v>4.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>-0.654</v>
+      </c>
+      <c r="L88">
+        <v>0.654</v>
+      </c>
+      <c r="M88">
+        <v>0.9009532</v>
+      </c>
+      <c r="N88">
+        <v>-0.2469532</v>
+      </c>
+      <c r="O88">
+        <v>-0.03704298000000003</v>
+      </c>
+      <c r="P88">
+        <v>-0.20991022</v>
+      </c>
+      <c r="Q88">
+        <v>-0.86391022</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5450604382020316</v>
+      </c>
+      <c r="T88">
+        <v>5.215046393692872</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.1088846790266132</v>
+      </c>
+      <c r="W88">
+        <v>0.1905204556241101</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.7258978601774211</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2419060531850191</v>
+      </c>
+      <c r="C89">
+        <v>-0.4853912688680122</v>
+      </c>
+      <c r="D89">
+        <v>1.667608731131988</v>
+      </c>
+      <c r="E89">
+        <v>4.263</v>
+      </c>
+      <c r="F89">
+        <v>4.263</v>
+      </c>
+      <c r="G89">
+        <v>2.11</v>
+      </c>
+      <c r="H89">
+        <v>4.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>-0.654</v>
+      </c>
+      <c r="L89">
+        <v>0.654</v>
+      </c>
+      <c r="M89">
+        <v>0.9114293999999999</v>
+      </c>
+      <c r="N89">
+        <v>-0.2574293999999999</v>
+      </c>
+      <c r="O89">
+        <v>-0.03861441000000002</v>
+      </c>
+      <c r="P89">
+        <v>-0.2188149899999999</v>
+      </c>
+      <c r="Q89">
+        <v>-0.87281499</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5840035488329571</v>
+      </c>
+      <c r="T89">
+        <v>5.616203808592323</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.1076331309918246</v>
+      </c>
+      <c r="W89">
+        <v>0.1907880365939479</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.7175542066121634</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2436560531850191</v>
+      </c>
+      <c r="C90">
+        <v>-0.5437376761804122</v>
+      </c>
+      <c r="D90">
+        <v>1.658262323819588</v>
+      </c>
+      <c r="E90">
+        <v>4.312</v>
+      </c>
+      <c r="F90">
+        <v>4.312</v>
+      </c>
+      <c r="G90">
+        <v>2.11</v>
+      </c>
+      <c r="H90">
+        <v>4.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>-0.654</v>
+      </c>
+      <c r="L90">
+        <v>0.654</v>
+      </c>
+      <c r="M90">
+        <v>0.9219056</v>
+      </c>
+      <c r="N90">
+        <v>-0.2679056</v>
+      </c>
+      <c r="O90">
+        <v>-0.04018584000000003</v>
+      </c>
+      <c r="P90">
+        <v>-0.2277197599999999</v>
+      </c>
+      <c r="Q90">
+        <v>-0.88171976</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6294371779023704</v>
+      </c>
+      <c r="T90">
+        <v>6.084220792641686</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.1064100272305539</v>
+      </c>
+      <c r="W90">
+        <v>0.1910495361781076</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.7094001815370251</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2454060531850191</v>
+      </c>
+      <c r="C91">
+        <v>-0.6019799002291739</v>
+      </c>
+      <c r="D91">
+        <v>1.649020099770827</v>
+      </c>
+      <c r="E91">
+        <v>4.361000000000001</v>
+      </c>
+      <c r="F91">
+        <v>4.361000000000001</v>
+      </c>
+      <c r="G91">
+        <v>2.11</v>
+      </c>
+      <c r="H91">
+        <v>4.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>-0.654</v>
+      </c>
+      <c r="L91">
+        <v>0.654</v>
+      </c>
+      <c r="M91">
+        <v>0.9323818000000001</v>
+      </c>
+      <c r="N91">
+        <v>-0.2783818000000001</v>
+      </c>
+      <c r="O91">
+        <v>-0.04175727000000005</v>
+      </c>
+      <c r="P91">
+        <v>-0.2366245300000001</v>
+      </c>
+      <c r="Q91">
+        <v>-0.8906245300000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6831314668025859</v>
+      </c>
+      <c r="T91">
+        <v>6.637331773790929</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.1052144089470645</v>
+      </c>
+      <c r="W91">
+        <v>0.1913051593671176</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.7014293929804292</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2471560531850191</v>
+      </c>
+      <c r="C92">
+        <v>-0.6601196733365242</v>
+      </c>
+      <c r="D92">
+        <v>1.639880326663476</v>
+      </c>
+      <c r="E92">
+        <v>4.41</v>
+      </c>
+      <c r="F92">
+        <v>4.41</v>
+      </c>
+      <c r="G92">
+        <v>2.11</v>
+      </c>
+      <c r="H92">
+        <v>4.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>-0.654</v>
+      </c>
+      <c r="L92">
+        <v>0.654</v>
+      </c>
+      <c r="M92">
+        <v>0.942858</v>
+      </c>
+      <c r="N92">
+        <v>-0.2888579999999999</v>
+      </c>
+      <c r="O92">
+        <v>-0.04332870000000003</v>
+      </c>
+      <c r="P92">
+        <v>-0.2455292999999999</v>
+      </c>
+      <c r="Q92">
+        <v>-0.8995293</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7475646134828444</v>
+      </c>
+      <c r="T92">
+        <v>7.301064951170023</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.1040453599587638</v>
+      </c>
+      <c r="W92">
+        <v>0.1915551020408163</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.6936357330584245</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2489060531850191</v>
+      </c>
+      <c r="C93">
+        <v>-0.7181586896304699</v>
+      </c>
+      <c r="D93">
+        <v>1.630841310369531</v>
+      </c>
+      <c r="E93">
+        <v>4.459000000000001</v>
+      </c>
+      <c r="F93">
+        <v>4.459000000000001</v>
+      </c>
+      <c r="G93">
+        <v>2.11</v>
+      </c>
+      <c r="H93">
+        <v>4.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>-0.654</v>
+      </c>
+      <c r="L93">
+        <v>0.654</v>
+      </c>
+      <c r="M93">
+        <v>0.9533342</v>
+      </c>
+      <c r="N93">
+        <v>-0.2993342</v>
+      </c>
+      <c r="O93">
+        <v>-0.04490013000000004</v>
+      </c>
+      <c r="P93">
+        <v>-0.25443407</v>
+      </c>
+      <c r="Q93">
+        <v>-0.90843407</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8263162372031607</v>
+      </c>
+      <c r="T93">
+        <v>8.112294390188916</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.1029020043548213</v>
+      </c>
+      <c r="W93">
+        <v>0.1917995514689392</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.6860133623654747</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2506560531850191</v>
+      </c>
+      <c r="C94">
+        <v>-0.7760986060916544</v>
+      </c>
+      <c r="D94">
+        <v>1.621901393908346</v>
+      </c>
+      <c r="E94">
+        <v>4.508000000000001</v>
+      </c>
+      <c r="F94">
+        <v>4.508000000000001</v>
+      </c>
+      <c r="G94">
+        <v>2.11</v>
+      </c>
+      <c r="H94">
+        <v>4.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>-0.654</v>
+      </c>
+      <c r="L94">
+        <v>0.654</v>
+      </c>
+      <c r="M94">
+        <v>0.9638104000000002</v>
+      </c>
+      <c r="N94">
+        <v>-0.3098104000000002</v>
+      </c>
+      <c r="O94">
+        <v>-0.04647156000000006</v>
+      </c>
+      <c r="P94">
+        <v>-0.2633388400000001</v>
+      </c>
+      <c r="Q94">
+        <v>-0.9173388400000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.924755766853556</v>
+      </c>
+      <c r="T94">
+        <v>9.126331188962531</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.1017835043074863</v>
+      </c>
+      <c r="W94">
+        <v>0.1920386867790594</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.6785566953832413</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2524060531850191</v>
+      </c>
+      <c r="C95">
+        <v>-0.8339410435659764</v>
+      </c>
+      <c r="D95">
+        <v>1.613058956434024</v>
+      </c>
+      <c r="E95">
+        <v>4.557</v>
+      </c>
+      <c r="F95">
+        <v>4.557</v>
+      </c>
+      <c r="G95">
+        <v>2.11</v>
+      </c>
+      <c r="H95">
+        <v>4.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>-0.654</v>
+      </c>
+      <c r="L95">
+        <v>0.654</v>
+      </c>
+      <c r="M95">
+        <v>0.9742866</v>
+      </c>
+      <c r="N95">
+        <v>-0.3202866</v>
+      </c>
+      <c r="O95">
+        <v>-0.04804299000000004</v>
+      </c>
+      <c r="P95">
+        <v>-0.2722436099999999</v>
+      </c>
+      <c r="Q95">
+        <v>-0.92624361</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.051320876404064</v>
+      </c>
+      <c r="T95">
+        <v>10.43009278738575</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.1006890580246101</v>
+      </c>
+      <c r="W95">
+        <v>0.1922726793943383</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.6712603868307334</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2541560531850191</v>
+      </c>
+      <c r="C96">
+        <v>-0.8916875877442676</v>
+      </c>
+      <c r="D96">
+        <v>1.604312412255733</v>
+      </c>
+      <c r="E96">
+        <v>4.606000000000001</v>
+      </c>
+      <c r="F96">
+        <v>4.606000000000001</v>
+      </c>
+      <c r="G96">
+        <v>2.11</v>
+      </c>
+      <c r="H96">
+        <v>4.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>-0.654</v>
+      </c>
+      <c r="L96">
+        <v>0.654</v>
+      </c>
+      <c r="M96">
+        <v>0.9847628000000002</v>
+      </c>
+      <c r="N96">
+        <v>-0.3307628000000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.04961442000000006</v>
+      </c>
+      <c r="P96">
+        <v>-0.2811483800000001</v>
+      </c>
+      <c r="Q96">
+        <v>-0.9351483800000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.220074355804742</v>
+      </c>
+      <c r="T96">
+        <v>12.16844158528338</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.09961789783285892</v>
+      </c>
+      <c r="W96">
+        <v>0.1925016934433348</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.6641193188857255</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2559060531850191</v>
+      </c>
+      <c r="C97">
+        <v>-0.9493397901102583</v>
+      </c>
+      <c r="D97">
+        <v>1.595660209889742</v>
+      </c>
+      <c r="E97">
+        <v>4.655</v>
+      </c>
+      <c r="F97">
+        <v>4.655</v>
+      </c>
+      <c r="G97">
+        <v>2.11</v>
+      </c>
+      <c r="H97">
+        <v>4.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>-0.654</v>
+      </c>
+      <c r="L97">
+        <v>0.654</v>
+      </c>
+      <c r="M97">
+        <v>0.995239</v>
+      </c>
+      <c r="N97">
+        <v>-0.341239</v>
+      </c>
+      <c r="O97">
+        <v>-0.05118585000000004</v>
+      </c>
+      <c r="P97">
+        <v>-0.2900531499999999</v>
+      </c>
+      <c r="Q97">
+        <v>-0.94405315</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.456329226965691</v>
+      </c>
+      <c r="T97">
+        <v>14.60212990234006</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.09856928838198672</v>
+      </c>
+      <c r="W97">
+        <v>0.1927258861439312</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.6571285892132444</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2576560531850191</v>
+      </c>
+      <c r="C98">
+        <v>-1.006899168858045</v>
+      </c>
+      <c r="D98">
+        <v>1.587100831141955</v>
+      </c>
+      <c r="E98">
+        <v>4.704</v>
+      </c>
+      <c r="F98">
+        <v>4.704</v>
+      </c>
+      <c r="G98">
+        <v>2.11</v>
+      </c>
+      <c r="H98">
+        <v>4.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>-0.654</v>
+      </c>
+      <c r="L98">
+        <v>0.654</v>
+      </c>
+      <c r="M98">
+        <v>1.0057152</v>
+      </c>
+      <c r="N98">
+        <v>-0.3517151999999998</v>
+      </c>
+      <c r="O98">
+        <v>-0.05275728000000002</v>
+      </c>
+      <c r="P98">
+        <v>-0.2989579199999998</v>
+      </c>
+      <c r="Q98">
+        <v>-0.9529579199999998</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.810711533707109</v>
+      </c>
+      <c r="T98">
+        <v>18.25266237792504</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.09754252496134104</v>
+      </c>
+      <c r="W98">
+        <v>0.1929454081632653</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.6502834997422731</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2594060531850191</v>
+      </c>
+      <c r="C99">
+        <v>-1.064367209780179</v>
+      </c>
+      <c r="D99">
+        <v>1.578632790219821</v>
+      </c>
+      <c r="E99">
+        <v>4.753</v>
+      </c>
+      <c r="F99">
+        <v>4.753</v>
+      </c>
+      <c r="G99">
+        <v>2.11</v>
+      </c>
+      <c r="H99">
+        <v>4.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>-0.654</v>
+      </c>
+      <c r="L99">
+        <v>0.654</v>
+      </c>
+      <c r="M99">
+        <v>1.0161914</v>
+      </c>
+      <c r="N99">
+        <v>-0.3621914000000001</v>
+      </c>
+      <c r="O99">
+        <v>-0.05432871000000006</v>
+      </c>
+      <c r="P99">
+        <v>-0.30786269</v>
+      </c>
+      <c r="Q99">
+        <v>-0.96186269</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.401348711609479</v>
+      </c>
+      <c r="T99">
+        <v>24.33688317056672</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.09653693192050246</v>
+      </c>
+      <c r="W99">
+        <v>0.1931604039553965</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.6435795461366824</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2611560531850191</v>
+      </c>
+      <c r="C100">
+        <v>-1.121745367127478</v>
+      </c>
+      <c r="D100">
+        <v>1.570254632872523</v>
+      </c>
+      <c r="E100">
+        <v>4.802</v>
+      </c>
+      <c r="F100">
+        <v>4.802</v>
+      </c>
+      <c r="G100">
+        <v>2.11</v>
+      </c>
+      <c r="H100">
+        <v>4.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>-0.654</v>
+      </c>
+      <c r="L100">
+        <v>0.654</v>
+      </c>
+      <c r="M100">
+        <v>1.0266676</v>
+      </c>
+      <c r="N100">
+        <v>-0.3726676000000001</v>
+      </c>
+      <c r="O100">
+        <v>-0.05590014000000006</v>
+      </c>
+      <c r="P100">
+        <v>-0.3167674600000001</v>
+      </c>
+      <c r="Q100">
+        <v>-0.97076746</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.582623067414219</v>
+      </c>
+      <c r="T100">
+        <v>36.50532475585008</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.09555186118661978</v>
+      </c>
+      <c r="W100">
+        <v>0.1933710120783007</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.6370124079107979</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2629060531850191</v>
+      </c>
+      <c r="C101">
+        <v>-1.179035064441599</v>
+      </c>
+      <c r="D101">
+        <v>1.561964935558401</v>
+      </c>
+      <c r="E101">
+        <v>4.851</v>
+      </c>
+      <c r="F101">
+        <v>4.851</v>
+      </c>
+      <c r="G101">
+        <v>2.11</v>
+      </c>
+      <c r="H101">
+        <v>4.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>-0.654</v>
+      </c>
+      <c r="L101">
+        <v>0.654</v>
+      </c>
+      <c r="M101">
+        <v>1.0371438</v>
+      </c>
+      <c r="N101">
+        <v>-0.3831437999999999</v>
+      </c>
+      <c r="O101">
+        <v>-0.05747157000000004</v>
+      </c>
+      <c r="P101">
+        <v>-0.3256722299999999</v>
+      </c>
+      <c r="Q101">
+        <v>-0.9796722299999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.126446134828438</v>
+      </c>
+      <c r="T101">
+        <v>73.01064951170015</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.09458669087160343</v>
+      </c>
+      <c r="W101">
+        <v>0.1935773654916512</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.6305779391440223</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
